--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125583945</v>
+        <v>125583954</v>
       </c>
       <c r="B2" t="n">
-        <v>78684</v>
+        <v>92646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528032</v>
+        <v>527986</v>
       </c>
       <c r="R2" t="n">
-        <v>7060391</v>
+        <v>7060380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125583874</v>
+        <v>125583910</v>
       </c>
       <c r="B3" t="n">
         <v>78683</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528145</v>
+        <v>528115</v>
       </c>
       <c r="R3" t="n">
-        <v>7060374</v>
+        <v>7060349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125583923</v>
+        <v>125583819</v>
       </c>
       <c r="B4" t="n">
-        <v>78683</v>
+        <v>92448</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528032</v>
+        <v>528247</v>
       </c>
       <c r="R4" t="n">
-        <v>7060391</v>
+        <v>7060540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +985,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125583910</v>
+        <v>125583923</v>
       </c>
       <c r="B5" t="n">
         <v>78683</v>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528115</v>
+        <v>528032</v>
       </c>
       <c r="R5" t="n">
-        <v>7060349</v>
+        <v>7060391</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125583966</v>
+        <v>125583900</v>
       </c>
       <c r="B6" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527984</v>
+        <v>528145</v>
       </c>
       <c r="R6" t="n">
-        <v>7060282</v>
+        <v>7060374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125583900</v>
+        <v>125583976</v>
       </c>
       <c r="B7" t="n">
         <v>78684</v>
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528145</v>
+        <v>527984</v>
       </c>
       <c r="R7" t="n">
-        <v>7060374</v>
+        <v>7060282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125583976</v>
+        <v>125583945</v>
       </c>
       <c r="B8" t="n">
         <v>78684</v>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527984</v>
+        <v>528032</v>
       </c>
       <c r="R8" t="n">
-        <v>7060282</v>
+        <v>7060391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125583819</v>
+        <v>125584089</v>
       </c>
       <c r="B10" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,42 +1507,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528247</v>
+        <v>527979</v>
       </c>
       <c r="R10" t="n">
-        <v>7060540</v>
+        <v>7060369</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125583954</v>
+        <v>125583874</v>
       </c>
       <c r="B11" t="n">
-        <v>92646</v>
+        <v>78683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527986</v>
+        <v>528145</v>
       </c>
       <c r="R11" t="n">
-        <v>7060380</v>
+        <v>7060374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125584089</v>
+        <v>125583966</v>
       </c>
       <c r="B12" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527979</v>
+        <v>527984</v>
       </c>
       <c r="R12" t="n">
-        <v>7060369</v>
+        <v>7060282</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598473</v>
+        <v>125598559</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>82737</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527959</v>
+        <v>528154</v>
       </c>
       <c r="R13" t="n">
-        <v>7060315</v>
+        <v>7060576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598453</v>
+        <v>125598538</v>
       </c>
       <c r="B14" t="n">
-        <v>96522</v>
+        <v>91326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528210</v>
+        <v>528219</v>
       </c>
       <c r="R14" t="n">
-        <v>7060528</v>
+        <v>7060602</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598479</v>
+        <v>125598480</v>
       </c>
       <c r="B15" t="n">
         <v>91166</v>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528026</v>
+        <v>528047</v>
       </c>
       <c r="R15" t="n">
-        <v>7060285</v>
+        <v>7060306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598573</v>
+        <v>125598469</v>
       </c>
       <c r="B16" t="n">
-        <v>92448</v>
+        <v>79536</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527916</v>
+        <v>528156</v>
       </c>
       <c r="R16" t="n">
-        <v>7060212</v>
+        <v>7060452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598565</v>
+        <v>125598483</v>
       </c>
       <c r="B17" t="n">
-        <v>91424</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,25 +2221,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528018</v>
+        <v>528196</v>
       </c>
       <c r="R17" t="n">
-        <v>7060178</v>
+        <v>7060457</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2285,6 +2285,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2311,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598568</v>
+        <v>125598558</v>
       </c>
       <c r="B18" t="n">
-        <v>92448</v>
+        <v>82737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528100</v>
+        <v>528156</v>
       </c>
       <c r="R18" t="n">
-        <v>7060507</v>
+        <v>7060663</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125598442</v>
+        <v>125598471</v>
       </c>
       <c r="B19" t="n">
-        <v>75025</v>
+        <v>79536</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2429,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528139</v>
+        <v>528115</v>
       </c>
       <c r="R19" t="n">
-        <v>7060573</v>
+        <v>7060370</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598532</v>
+        <v>125598571</v>
       </c>
       <c r="B20" t="n">
-        <v>78683</v>
+        <v>92448</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528019</v>
+        <v>527968</v>
       </c>
       <c r="R20" t="n">
-        <v>7060293</v>
+        <v>7060326</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598540</v>
+        <v>125598551</v>
       </c>
       <c r="B21" t="n">
-        <v>91326</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528139</v>
+        <v>528012</v>
       </c>
       <c r="R21" t="n">
-        <v>7060421</v>
+        <v>7060230</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125598464</v>
+        <v>125598531</v>
       </c>
       <c r="B22" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2735,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528013</v>
+        <v>527988</v>
       </c>
       <c r="R22" t="n">
-        <v>7060176</v>
+        <v>7060369</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125598530</v>
+        <v>125598464</v>
       </c>
       <c r="B23" t="n">
-        <v>78683</v>
+        <v>79565</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2837,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2861,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528109</v>
+        <v>528013</v>
       </c>
       <c r="R23" t="n">
-        <v>7060312</v>
+        <v>7060176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125598484</v>
+        <v>125598552</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2939,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528028</v>
+        <v>527891</v>
       </c>
       <c r="R24" t="n">
-        <v>7060282</v>
+        <v>7060221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,11 +3004,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598558</v>
+        <v>125598463</v>
       </c>
       <c r="B25" t="n">
-        <v>82737</v>
+        <v>79565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528156</v>
+        <v>527988</v>
       </c>
       <c r="R25" t="n">
-        <v>7060663</v>
+        <v>7060368</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598550</v>
+        <v>125598541</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
+        <v>91326</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3144,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528067</v>
+        <v>528123</v>
       </c>
       <c r="R26" t="n">
-        <v>7060280</v>
+        <v>7060390</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598578</v>
+        <v>125598473</v>
       </c>
       <c r="B27" t="n">
-        <v>77874</v>
+        <v>79536</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528105</v>
+        <v>527959</v>
       </c>
       <c r="R27" t="n">
-        <v>7060313</v>
+        <v>7060315</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598463</v>
+        <v>125598532</v>
       </c>
       <c r="B28" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527988</v>
+        <v>528019</v>
       </c>
       <c r="R28" t="n">
-        <v>7060368</v>
+        <v>7060293</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598445</v>
+        <v>125598479</v>
       </c>
       <c r="B29" t="n">
-        <v>75025</v>
+        <v>91166</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527906</v>
+        <v>528026</v>
       </c>
       <c r="R29" t="n">
-        <v>7060232</v>
+        <v>7060285</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598541</v>
+        <v>125598549</v>
       </c>
       <c r="B30" t="n">
-        <v>91326</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,25 +3552,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528123</v>
+        <v>528054</v>
       </c>
       <c r="R30" t="n">
-        <v>7060390</v>
+        <v>7060352</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598471</v>
+        <v>125598547</v>
       </c>
       <c r="B31" t="n">
-        <v>79536</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528115</v>
+        <v>528196</v>
       </c>
       <c r="R31" t="n">
-        <v>7060370</v>
+        <v>7060721</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598480</v>
+        <v>125598517</v>
       </c>
       <c r="B32" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528047</v>
+        <v>528033</v>
       </c>
       <c r="R32" t="n">
-        <v>7060306</v>
+        <v>7060297</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598533</v>
+        <v>125598445</v>
       </c>
       <c r="B33" t="n">
-        <v>78683</v>
+        <v>75025</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527893</v>
+        <v>527906</v>
       </c>
       <c r="R33" t="n">
-        <v>7060200</v>
+        <v>7060232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598572</v>
+        <v>125598485</v>
       </c>
       <c r="B34" t="n">
-        <v>92448</v>
+        <v>57635</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3960,25 +3960,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528018</v>
+        <v>528035</v>
       </c>
       <c r="R34" t="n">
-        <v>7060189</v>
+        <v>7060278</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4024,6 +4024,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4050,10 +4055,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598470</v>
+        <v>125598572</v>
       </c>
       <c r="B35" t="n">
-        <v>79536</v>
+        <v>92448</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4062,25 +4067,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4095,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528137</v>
+        <v>528018</v>
       </c>
       <c r="R35" t="n">
-        <v>7060400</v>
+        <v>7060189</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4157,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598542</v>
+        <v>125598568</v>
       </c>
       <c r="B36" t="n">
-        <v>91326</v>
+        <v>92448</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4164,25 +4169,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4197,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527984</v>
+        <v>528100</v>
       </c>
       <c r="R36" t="n">
-        <v>7060358</v>
+        <v>7060507</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4259,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598483</v>
+        <v>125598567</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
+        <v>92448</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4266,25 +4271,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4299,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528196</v>
+        <v>528156</v>
       </c>
       <c r="R37" t="n">
-        <v>7060457</v>
+        <v>7060538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4330,11 +4335,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598569</v>
+        <v>125598539</v>
       </c>
       <c r="B38" t="n">
-        <v>92448</v>
+        <v>91326</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4373,25 +4373,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528105</v>
+        <v>528155</v>
       </c>
       <c r="R38" t="n">
-        <v>7060384</v>
+        <v>7060497</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598567</v>
+        <v>125598470</v>
       </c>
       <c r="B39" t="n">
-        <v>92448</v>
+        <v>79536</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,25 +4475,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528156</v>
+        <v>528137</v>
       </c>
       <c r="R39" t="n">
-        <v>7060538</v>
+        <v>7060400</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598571</v>
+        <v>125598474</v>
       </c>
       <c r="B40" t="n">
-        <v>92448</v>
+        <v>79536</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,25 +4577,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527968</v>
+        <v>528004</v>
       </c>
       <c r="R40" t="n">
-        <v>7060326</v>
+        <v>7060217</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598462</v>
+        <v>125598565</v>
       </c>
       <c r="B41" t="n">
-        <v>79565</v>
+        <v>91424</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,25 +4679,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528155</v>
+        <v>528018</v>
       </c>
       <c r="R41" t="n">
-        <v>7060516</v>
+        <v>7060178</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598508</v>
+        <v>125598578</v>
       </c>
       <c r="B42" t="n">
-        <v>80029</v>
+        <v>77874</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4785,21 +4785,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528116</v>
+        <v>528105</v>
       </c>
       <c r="R42" t="n">
-        <v>7060509</v>
+        <v>7060313</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,10 +4871,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598474</v>
+        <v>125598478</v>
       </c>
       <c r="B43" t="n">
-        <v>79536</v>
+        <v>91166</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4887,21 +4887,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528004</v>
+        <v>528153</v>
       </c>
       <c r="R43" t="n">
-        <v>7060217</v>
+        <v>7060642</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598559</v>
+        <v>125598484</v>
       </c>
       <c r="B44" t="n">
-        <v>82737</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4989,21 +4989,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528154</v>
+        <v>528028</v>
       </c>
       <c r="R44" t="n">
-        <v>7060576</v>
+        <v>7060282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5049,6 +5049,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,10 +5080,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598517</v>
+        <v>125598462</v>
       </c>
       <c r="B45" t="n">
-        <v>91459</v>
+        <v>79565</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5091,21 +5096,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528033</v>
+        <v>528155</v>
       </c>
       <c r="R45" t="n">
-        <v>7060297</v>
+        <v>7060516</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5177,10 +5182,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598531</v>
+        <v>125598472</v>
       </c>
       <c r="B46" t="n">
-        <v>78683</v>
+        <v>79536</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5193,21 +5198,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527988</v>
+        <v>528108</v>
       </c>
       <c r="R46" t="n">
-        <v>7060369</v>
+        <v>7060311</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5279,10 +5284,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598472</v>
+        <v>125598564</v>
       </c>
       <c r="B47" t="n">
-        <v>79536</v>
+        <v>91424</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5291,25 +5296,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5319,10 +5324,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528108</v>
+        <v>528199</v>
       </c>
       <c r="R47" t="n">
-        <v>7060311</v>
+        <v>7060578</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5381,7 +5386,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598538</v>
+        <v>125598542</v>
       </c>
       <c r="B48" t="n">
         <v>91326</v>
@@ -5421,10 +5426,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528219</v>
+        <v>527984</v>
       </c>
       <c r="R48" t="n">
-        <v>7060602</v>
+        <v>7060358</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5483,10 +5488,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598564</v>
+        <v>125598442</v>
       </c>
       <c r="B49" t="n">
-        <v>91424</v>
+        <v>75025</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5495,25 +5500,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5523,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528199</v>
+        <v>528139</v>
       </c>
       <c r="R49" t="n">
-        <v>7060578</v>
+        <v>7060573</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5585,10 +5590,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598551</v>
+        <v>125598443</v>
       </c>
       <c r="B50" t="n">
-        <v>78947</v>
+        <v>75025</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5601,21 +5606,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5625,10 +5630,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528012</v>
+        <v>528204</v>
       </c>
       <c r="R50" t="n">
-        <v>7060230</v>
+        <v>7060474</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5687,10 +5692,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598443</v>
+        <v>125598569</v>
       </c>
       <c r="B51" t="n">
-        <v>75025</v>
+        <v>92448</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5699,25 +5704,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5727,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528204</v>
+        <v>528105</v>
       </c>
       <c r="R51" t="n">
-        <v>7060474</v>
+        <v>7060384</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5789,10 +5794,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598513</v>
+        <v>125598560</v>
       </c>
       <c r="B52" t="n">
-        <v>79932</v>
+        <v>82737</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5801,25 +5806,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5829,10 +5834,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528117</v>
+        <v>527902</v>
       </c>
       <c r="R52" t="n">
-        <v>7060478</v>
+        <v>7060225</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5891,10 +5896,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125598478</v>
+        <v>125598530</v>
       </c>
       <c r="B53" t="n">
-        <v>91166</v>
+        <v>78683</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5907,21 +5912,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5931,10 +5936,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528153</v>
+        <v>528109</v>
       </c>
       <c r="R53" t="n">
-        <v>7060642</v>
+        <v>7060312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,10 +5998,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598547</v>
+        <v>125598506</v>
       </c>
       <c r="B54" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6009,34 +6014,50 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528196</v>
+        <v>528169</v>
       </c>
       <c r="R54" t="n">
-        <v>7060721</v>
+        <v>7060483</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6095,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598552</v>
+        <v>125598508</v>
       </c>
       <c r="B55" t="n">
-        <v>78947</v>
+        <v>80029</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6111,21 +6132,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6135,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527891</v>
+        <v>528116</v>
       </c>
       <c r="R55" t="n">
-        <v>7060221</v>
+        <v>7060509</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6197,10 +6218,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598469</v>
+        <v>125598533</v>
       </c>
       <c r="B56" t="n">
-        <v>79536</v>
+        <v>78683</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6213,21 +6234,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6237,10 +6258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528156</v>
+        <v>527893</v>
       </c>
       <c r="R56" t="n">
-        <v>7060452</v>
+        <v>7060200</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6299,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598506</v>
+        <v>125598550</v>
       </c>
       <c r="B57" t="n">
-        <v>57793</v>
+        <v>78947</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6315,50 +6336,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528169</v>
+        <v>528067</v>
       </c>
       <c r="R57" t="n">
-        <v>7060483</v>
+        <v>7060280</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6417,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598485</v>
+        <v>125598513</v>
       </c>
       <c r="B58" t="n">
-        <v>57635</v>
+        <v>79932</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6429,25 +6434,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6457,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528035</v>
+        <v>528117</v>
       </c>
       <c r="R58" t="n">
-        <v>7060278</v>
+        <v>7060478</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6493,11 +6498,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6524,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125598549</v>
+        <v>125598453</v>
       </c>
       <c r="B59" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528054</v>
+        <v>528210</v>
       </c>
       <c r="R59" t="n">
-        <v>7060352</v>
+        <v>7060528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125598539</v>
+        <v>125598573</v>
       </c>
       <c r="B60" t="n">
-        <v>91326</v>
+        <v>92448</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6638,25 +6638,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528155</v>
+        <v>527916</v>
       </c>
       <c r="R60" t="n">
-        <v>7060497</v>
+        <v>7060212</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125598560</v>
+        <v>125598540</v>
       </c>
       <c r="B61" t="n">
-        <v>82737</v>
+        <v>91326</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6740,25 +6740,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527902</v>
+        <v>528139</v>
       </c>
       <c r="R61" t="n">
-        <v>7060225</v>
+        <v>7060421</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -1746,10 +1746,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598443</v>
+        <v>125598474</v>
       </c>
       <c r="B13" t="n">
-        <v>75066</v>
+        <v>79556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528204</v>
+        <v>528004</v>
       </c>
       <c r="R13" t="n">
-        <v>7060474</v>
+        <v>7060217</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598569</v>
+        <v>125598443</v>
       </c>
       <c r="B14" t="n">
-        <v>92502</v>
+        <v>75066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528105</v>
+        <v>528204</v>
       </c>
       <c r="R14" t="n">
-        <v>7060384</v>
+        <v>7060474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598442</v>
+        <v>125598569</v>
       </c>
       <c r="B15" t="n">
-        <v>75066</v>
+        <v>92502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528139</v>
+        <v>528105</v>
       </c>
       <c r="R15" t="n">
-        <v>7060573</v>
+        <v>7060384</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,32 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598540</v>
+        <v>125598442</v>
       </c>
       <c r="B16" t="n">
-        <v>91380</v>
+        <v>75066</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
         <v>528139</v>
       </c>
       <c r="R16" t="n">
-        <v>7060421</v>
+        <v>7060573</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,32 +2134,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598549</v>
+        <v>125598540</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>91380</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528054</v>
+        <v>528139</v>
       </c>
       <c r="R17" t="n">
-        <v>7060352</v>
+        <v>7060421</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598474</v>
+        <v>125598549</v>
       </c>
       <c r="B18" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528004</v>
+        <v>528054</v>
       </c>
       <c r="R18" t="n">
-        <v>7060217</v>
+        <v>7060352</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B31" t="n">
-        <v>57811</v>
+        <v>78725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,50 +3503,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R31" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3589,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B32" t="n">
-        <v>78725</v>
+        <v>57811</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,34 +3600,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R32" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>125583954</v>
       </c>
       <c r="B8" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125583819</v>
       </c>
       <c r="B11" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598474</v>
+        <v>125598443</v>
       </c>
       <c r="B13" t="n">
-        <v>79556</v>
+        <v>75066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528004</v>
+        <v>528204</v>
       </c>
       <c r="R13" t="n">
-        <v>7060217</v>
+        <v>7060474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598443</v>
+        <v>125598569</v>
       </c>
       <c r="B14" t="n">
-        <v>75066</v>
+        <v>92509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528204</v>
+        <v>528105</v>
       </c>
       <c r="R14" t="n">
-        <v>7060474</v>
+        <v>7060384</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598569</v>
+        <v>125598442</v>
       </c>
       <c r="B15" t="n">
-        <v>92502</v>
+        <v>75066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528105</v>
+        <v>528139</v>
       </c>
       <c r="R15" t="n">
-        <v>7060384</v>
+        <v>7060573</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,32 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598442</v>
+        <v>125598540</v>
       </c>
       <c r="B16" t="n">
-        <v>75066</v>
+        <v>91387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
         <v>528139</v>
       </c>
       <c r="R16" t="n">
-        <v>7060573</v>
+        <v>7060421</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,32 +2134,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598540</v>
+        <v>125598549</v>
       </c>
       <c r="B17" t="n">
-        <v>91380</v>
+        <v>78967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528139</v>
+        <v>528054</v>
       </c>
       <c r="R17" t="n">
-        <v>7060421</v>
+        <v>7060352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598549</v>
+        <v>125598474</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528054</v>
+        <v>528004</v>
       </c>
       <c r="R18" t="n">
-        <v>7060352</v>
+        <v>7060217</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,32 +2425,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598445</v>
+        <v>125598568</v>
       </c>
       <c r="B20" t="n">
-        <v>75066</v>
+        <v>92509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527906</v>
+        <v>528100</v>
       </c>
       <c r="R20" t="n">
-        <v>7060232</v>
+        <v>7060507</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2522,32 +2522,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598568</v>
+        <v>125598445</v>
       </c>
       <c r="B21" t="n">
-        <v>92502</v>
+        <v>75066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528100</v>
+        <v>527906</v>
       </c>
       <c r="R21" t="n">
-        <v>7060507</v>
+        <v>7060232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,7 +2719,7 @@
         <v>125598538</v>
       </c>
       <c r="B23" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>125598567</v>
       </c>
       <c r="B24" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>125598573</v>
       </c>
       <c r="B27" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>125598478</v>
       </c>
       <c r="B29" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B31" t="n">
-        <v>78725</v>
+        <v>57811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,34 +3503,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R31" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B32" t="n">
-        <v>57811</v>
+        <v>78725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3600,50 +3616,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R32" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3705,7 +3705,7 @@
         <v>125598565</v>
       </c>
       <c r="B33" t="n">
-        <v>91478</v>
+        <v>91485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>125598571</v>
       </c>
       <c r="B35" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>125598453</v>
       </c>
       <c r="B39" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>125598539</v>
       </c>
       <c r="B40" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>125598479</v>
       </c>
       <c r="B42" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>125598564</v>
       </c>
       <c r="B44" t="n">
-        <v>91478</v>
+        <v>91485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>125598517</v>
       </c>
       <c r="B45" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>125598480</v>
       </c>
       <c r="B46" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>125598572</v>
       </c>
       <c r="B52" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>125598542</v>
       </c>
       <c r="B57" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>125598541</v>
       </c>
       <c r="B58" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -3007,10 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598530</v>
+        <v>125598472</v>
       </c>
       <c r="B26" t="n">
-        <v>78725</v>
+        <v>79556</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528109</v>
+        <v>528108</v>
       </c>
       <c r="R26" t="n">
-        <v>7060312</v>
+        <v>7060311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598573</v>
+        <v>125598530</v>
       </c>
       <c r="B27" t="n">
-        <v>92509</v>
+        <v>78725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527916</v>
+        <v>528109</v>
       </c>
       <c r="R27" t="n">
-        <v>7060212</v>
+        <v>7060312</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,10 +3201,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598513</v>
+        <v>125598573</v>
       </c>
       <c r="B28" t="n">
-        <v>79974</v>
+        <v>92509</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3212,21 +3212,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528117</v>
+        <v>527916</v>
       </c>
       <c r="R28" t="n">
-        <v>7060478</v>
+        <v>7060212</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,32 +3298,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598478</v>
+        <v>125598513</v>
       </c>
       <c r="B29" t="n">
-        <v>91227</v>
+        <v>79974</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528153</v>
+        <v>528117</v>
       </c>
       <c r="R29" t="n">
-        <v>7060642</v>
+        <v>7060478</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598472</v>
+        <v>125598478</v>
       </c>
       <c r="B30" t="n">
-        <v>79556</v>
+        <v>91227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528108</v>
+        <v>528153</v>
       </c>
       <c r="R30" t="n">
-        <v>7060311</v>
+        <v>7060642</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B31" t="n">
-        <v>57811</v>
+        <v>78725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,50 +3503,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R31" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3589,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B32" t="n">
-        <v>78725</v>
+        <v>57811</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,34 +3600,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R32" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4769,32 +4769,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598564</v>
+        <v>125598471</v>
       </c>
       <c r="B44" t="n">
-        <v>91485</v>
+        <v>79556</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528199</v>
+        <v>528115</v>
       </c>
       <c r="R44" t="n">
-        <v>7060578</v>
+        <v>7060370</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598517</v>
+        <v>125598469</v>
       </c>
       <c r="B45" t="n">
-        <v>91520</v>
+        <v>79556</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528033</v>
+        <v>528156</v>
       </c>
       <c r="R45" t="n">
-        <v>7060297</v>
+        <v>7060452</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598480</v>
+        <v>125598564</v>
       </c>
       <c r="B46" t="n">
-        <v>91227</v>
+        <v>91485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528047</v>
+        <v>528199</v>
       </c>
       <c r="R46" t="n">
-        <v>7060306</v>
+        <v>7060578</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598532</v>
+        <v>125598517</v>
       </c>
       <c r="B47" t="n">
-        <v>78725</v>
+        <v>91520</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528019</v>
+        <v>528033</v>
       </c>
       <c r="R47" t="n">
-        <v>7060293</v>
+        <v>7060297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598471</v>
+        <v>125598480</v>
       </c>
       <c r="B48" t="n">
-        <v>79556</v>
+        <v>91227</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528115</v>
+        <v>528047</v>
       </c>
       <c r="R48" t="n">
-        <v>7060370</v>
+        <v>7060306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598469</v>
+        <v>125598532</v>
       </c>
       <c r="B49" t="n">
-        <v>79556</v>
+        <v>78725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528156</v>
+        <v>528019</v>
       </c>
       <c r="R49" t="n">
-        <v>7060452</v>
+        <v>7060293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -3007,10 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598472</v>
+        <v>125598530</v>
       </c>
       <c r="B26" t="n">
-        <v>79556</v>
+        <v>78725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528108</v>
+        <v>528109</v>
       </c>
       <c r="R26" t="n">
-        <v>7060311</v>
+        <v>7060312</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598530</v>
+        <v>125598573</v>
       </c>
       <c r="B27" t="n">
-        <v>78725</v>
+        <v>92509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528109</v>
+        <v>527916</v>
       </c>
       <c r="R27" t="n">
-        <v>7060312</v>
+        <v>7060212</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,10 +3201,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598573</v>
+        <v>125598513</v>
       </c>
       <c r="B28" t="n">
-        <v>92509</v>
+        <v>79974</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3212,21 +3212,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527916</v>
+        <v>528117</v>
       </c>
       <c r="R28" t="n">
-        <v>7060212</v>
+        <v>7060478</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,32 +3298,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598513</v>
+        <v>125598478</v>
       </c>
       <c r="B29" t="n">
-        <v>79974</v>
+        <v>91227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528117</v>
+        <v>528153</v>
       </c>
       <c r="R29" t="n">
-        <v>7060478</v>
+        <v>7060642</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598478</v>
+        <v>125598472</v>
       </c>
       <c r="B30" t="n">
-        <v>91227</v>
+        <v>79556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528153</v>
+        <v>528108</v>
       </c>
       <c r="R30" t="n">
-        <v>7060642</v>
+        <v>7060311</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B31" t="n">
-        <v>78725</v>
+        <v>57811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,34 +3503,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R31" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B32" t="n">
-        <v>57811</v>
+        <v>78725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3600,50 +3616,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R32" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598473</v>
+        <v>125598479</v>
       </c>
       <c r="B41" t="n">
-        <v>79556</v>
+        <v>91227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527959</v>
+        <v>528026</v>
       </c>
       <c r="R41" t="n">
-        <v>7060315</v>
+        <v>7060285</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598479</v>
+        <v>125598552</v>
       </c>
       <c r="B42" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528026</v>
+        <v>527891</v>
       </c>
       <c r="R42" t="n">
-        <v>7060285</v>
+        <v>7060221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598552</v>
+        <v>125598473</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527891</v>
+        <v>527959</v>
       </c>
       <c r="R43" t="n">
-        <v>7060221</v>
+        <v>7060315</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598470</v>
+        <v>125598550</v>
       </c>
       <c r="B54" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528137</v>
+        <v>528067</v>
       </c>
       <c r="R54" t="n">
-        <v>7060400</v>
+        <v>7060280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598550</v>
+        <v>125598464</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528067</v>
+        <v>528013</v>
       </c>
       <c r="R55" t="n">
-        <v>7060280</v>
+        <v>7060176</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598464</v>
+        <v>125598470</v>
       </c>
       <c r="B56" t="n">
-        <v>79585</v>
+        <v>79556</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5944,21 +5944,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528013</v>
+        <v>528137</v>
       </c>
       <c r="R56" t="n">
-        <v>7060176</v>
+        <v>7060400</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125583945</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125583900</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125583874</v>
       </c>
       <c r="B4" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125584089</v>
       </c>
       <c r="B5" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125583923</v>
       </c>
       <c r="B6" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125583976</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125583954</v>
       </c>
       <c r="B8" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125583966</v>
       </c>
       <c r="B9" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125583851</v>
       </c>
       <c r="B10" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125583819</v>
       </c>
       <c r="B11" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>125583910</v>
       </c>
       <c r="B12" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125598443</v>
       </c>
       <c r="B13" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>125598569</v>
       </c>
       <c r="B14" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>125598442</v>
       </c>
       <c r="B15" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,32 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598540</v>
+        <v>125598549</v>
       </c>
       <c r="B16" t="n">
-        <v>91387</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528139</v>
+        <v>528054</v>
       </c>
       <c r="R16" t="n">
-        <v>7060421</v>
+        <v>7060352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,32 +2134,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598549</v>
+        <v>125598540</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>91389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528054</v>
+        <v>528139</v>
       </c>
       <c r="R17" t="n">
-        <v>7060352</v>
+        <v>7060421</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2234,7 +2234,7 @@
         <v>125598474</v>
       </c>
       <c r="B18" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>125598547</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>125598568</v>
       </c>
       <c r="B20" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>125598445</v>
       </c>
       <c r="B21" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125598578</v>
+        <v>125598567</v>
       </c>
       <c r="B22" t="n">
-        <v>77916</v>
+        <v>92518</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528105</v>
+        <v>528156</v>
       </c>
       <c r="R22" t="n">
-        <v>7060313</v>
+        <v>7060538</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,32 +2716,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125598538</v>
+        <v>125598462</v>
       </c>
       <c r="B23" t="n">
-        <v>91387</v>
+        <v>79586</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528219</v>
+        <v>528155</v>
       </c>
       <c r="R23" t="n">
-        <v>7060602</v>
+        <v>7060516</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,32 +2813,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125598567</v>
+        <v>125598538</v>
       </c>
       <c r="B24" t="n">
-        <v>92509</v>
+        <v>91389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528156</v>
+        <v>528219</v>
       </c>
       <c r="R24" t="n">
-        <v>7060538</v>
+        <v>7060602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598462</v>
+        <v>125598578</v>
       </c>
       <c r="B25" t="n">
-        <v>79585</v>
+        <v>77917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,21 +2921,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528155</v>
+        <v>528105</v>
       </c>
       <c r="R25" t="n">
-        <v>7060516</v>
+        <v>7060313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598530</v>
+        <v>125598472</v>
       </c>
       <c r="B26" t="n">
-        <v>78725</v>
+        <v>79557</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528109</v>
+        <v>528108</v>
       </c>
       <c r="R26" t="n">
-        <v>7060312</v>
+        <v>7060311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598573</v>
+        <v>125598530</v>
       </c>
       <c r="B27" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527916</v>
+        <v>528109</v>
       </c>
       <c r="R27" t="n">
-        <v>7060212</v>
+        <v>7060312</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,10 +3201,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598513</v>
+        <v>125598573</v>
       </c>
       <c r="B28" t="n">
-        <v>79974</v>
+        <v>92518</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3212,21 +3212,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528117</v>
+        <v>527916</v>
       </c>
       <c r="R28" t="n">
-        <v>7060478</v>
+        <v>7060212</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,32 +3298,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598478</v>
+        <v>125598513</v>
       </c>
       <c r="B29" t="n">
-        <v>91227</v>
+        <v>79975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528153</v>
+        <v>528117</v>
       </c>
       <c r="R29" t="n">
-        <v>7060642</v>
+        <v>7060478</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598472</v>
+        <v>125598478</v>
       </c>
       <c r="B30" t="n">
-        <v>79556</v>
+        <v>91228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528108</v>
+        <v>528153</v>
       </c>
       <c r="R30" t="n">
-        <v>7060311</v>
+        <v>7060642</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3608,7 +3608,7 @@
         <v>125598533</v>
       </c>
       <c r="B32" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>125598565</v>
       </c>
       <c r="B33" t="n">
-        <v>91485</v>
+        <v>91489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,32 +3799,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598560</v>
+        <v>125598571</v>
       </c>
       <c r="B34" t="n">
-        <v>82779</v>
+        <v>92518</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527902</v>
+        <v>527968</v>
       </c>
       <c r="R34" t="n">
-        <v>7060225</v>
+        <v>7060326</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,32 +3896,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598571</v>
+        <v>125598560</v>
       </c>
       <c r="B35" t="n">
-        <v>92509</v>
+        <v>82780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527968</v>
+        <v>527902</v>
       </c>
       <c r="R35" t="n">
-        <v>7060326</v>
+        <v>7060225</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,10 +3993,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598531</v>
+        <v>125598559</v>
       </c>
       <c r="B36" t="n">
-        <v>78725</v>
+        <v>82780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4004,21 +4004,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527988</v>
+        <v>528154</v>
       </c>
       <c r="R36" t="n">
-        <v>7060369</v>
+        <v>7060576</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,10 +4090,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598559</v>
+        <v>125598531</v>
       </c>
       <c r="B37" t="n">
-        <v>82779</v>
+        <v>78726</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4101,21 +4101,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528154</v>
+        <v>527988</v>
       </c>
       <c r="R37" t="n">
-        <v>7060576</v>
+        <v>7060369</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
         <v>125598551</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>125598453</v>
       </c>
       <c r="B39" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>125598539</v>
       </c>
       <c r="B40" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598479</v>
+        <v>125598552</v>
       </c>
       <c r="B41" t="n">
-        <v>91227</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528026</v>
+        <v>527891</v>
       </c>
       <c r="R41" t="n">
-        <v>7060285</v>
+        <v>7060221</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598552</v>
+        <v>125598479</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>91228</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527891</v>
+        <v>528026</v>
       </c>
       <c r="R42" t="n">
-        <v>7060221</v>
+        <v>7060285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4675,7 +4675,7 @@
         <v>125598473</v>
       </c>
       <c r="B43" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>125598471</v>
       </c>
       <c r="B44" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>125598469</v>
       </c>
       <c r="B45" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598564</v>
+        <v>125598532</v>
       </c>
       <c r="B46" t="n">
-        <v>91485</v>
+        <v>78726</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528199</v>
+        <v>528019</v>
       </c>
       <c r="R46" t="n">
-        <v>7060578</v>
+        <v>7060293</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,32 +5060,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598517</v>
+        <v>125598564</v>
       </c>
       <c r="B47" t="n">
-        <v>91520</v>
+        <v>91489</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528033</v>
+        <v>528199</v>
       </c>
       <c r="R47" t="n">
-        <v>7060297</v>
+        <v>7060578</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598480</v>
+        <v>125598517</v>
       </c>
       <c r="B48" t="n">
-        <v>91227</v>
+        <v>91524</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528047</v>
+        <v>528033</v>
       </c>
       <c r="R48" t="n">
-        <v>7060306</v>
+        <v>7060297</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598532</v>
+        <v>125598480</v>
       </c>
       <c r="B49" t="n">
-        <v>78725</v>
+        <v>91228</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528019</v>
+        <v>528047</v>
       </c>
       <c r="R49" t="n">
-        <v>7060293</v>
+        <v>7060306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598558</v>
+        <v>125598463</v>
       </c>
       <c r="B50" t="n">
-        <v>82779</v>
+        <v>79586</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528156</v>
+        <v>527988</v>
       </c>
       <c r="R50" t="n">
-        <v>7060663</v>
+        <v>7060368</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598463</v>
+        <v>125598558</v>
       </c>
       <c r="B51" t="n">
-        <v>79585</v>
+        <v>82780</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527988</v>
+        <v>528156</v>
       </c>
       <c r="R51" t="n">
-        <v>7060368</v>
+        <v>7060663</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5548,7 +5548,7 @@
         <v>125598572</v>
       </c>
       <c r="B52" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>125598508</v>
       </c>
       <c r="B53" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>125598550</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>125598464</v>
       </c>
       <c r="B55" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>125598470</v>
       </c>
       <c r="B56" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>125598542</v>
       </c>
       <c r="B57" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>125598541</v>
       </c>
       <c r="B58" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -3007,10 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598472</v>
+        <v>125598530</v>
       </c>
       <c r="B26" t="n">
-        <v>79557</v>
+        <v>78726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528108</v>
+        <v>528109</v>
       </c>
       <c r="R26" t="n">
-        <v>7060311</v>
+        <v>7060312</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598530</v>
+        <v>125598573</v>
       </c>
       <c r="B27" t="n">
-        <v>78726</v>
+        <v>92518</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528109</v>
+        <v>527916</v>
       </c>
       <c r="R27" t="n">
-        <v>7060312</v>
+        <v>7060212</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,10 +3201,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598573</v>
+        <v>125598513</v>
       </c>
       <c r="B28" t="n">
-        <v>92518</v>
+        <v>79975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3212,21 +3212,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527916</v>
+        <v>528117</v>
       </c>
       <c r="R28" t="n">
-        <v>7060212</v>
+        <v>7060478</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,32 +3298,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598513</v>
+        <v>125598478</v>
       </c>
       <c r="B29" t="n">
-        <v>79975</v>
+        <v>91228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528117</v>
+        <v>528153</v>
       </c>
       <c r="R29" t="n">
-        <v>7060478</v>
+        <v>7060642</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598478</v>
+        <v>125598472</v>
       </c>
       <c r="B30" t="n">
-        <v>91228</v>
+        <v>79557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528153</v>
+        <v>528108</v>
       </c>
       <c r="R30" t="n">
-        <v>7060642</v>
+        <v>7060311</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B31" t="n">
-        <v>57811</v>
+        <v>78726</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,50 +3503,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R31" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3589,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B32" t="n">
-        <v>78726</v>
+        <v>57811</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,34 +3600,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R32" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598551</v>
+        <v>125598453</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>96587</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4198,21 +4198,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528012</v>
+        <v>528210</v>
       </c>
       <c r="R38" t="n">
-        <v>7060230</v>
+        <v>7060528</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598453</v>
+        <v>125598551</v>
       </c>
       <c r="B39" t="n">
-        <v>96587</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528210</v>
+        <v>528012</v>
       </c>
       <c r="R39" t="n">
-        <v>7060528</v>
+        <v>7060230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598552</v>
+        <v>125598473</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>79557</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527891</v>
+        <v>527959</v>
       </c>
       <c r="R41" t="n">
-        <v>7060221</v>
+        <v>7060315</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598479</v>
+        <v>125598552</v>
       </c>
       <c r="B42" t="n">
-        <v>91228</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528026</v>
+        <v>527891</v>
       </c>
       <c r="R42" t="n">
-        <v>7060285</v>
+        <v>7060221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598473</v>
+        <v>125598479</v>
       </c>
       <c r="B43" t="n">
-        <v>79557</v>
+        <v>91228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527959</v>
+        <v>528026</v>
       </c>
       <c r="R43" t="n">
-        <v>7060315</v>
+        <v>7060285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598471</v>
+        <v>125598532</v>
       </c>
       <c r="B44" t="n">
-        <v>79557</v>
+        <v>78726</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528115</v>
+        <v>528019</v>
       </c>
       <c r="R44" t="n">
-        <v>7060370</v>
+        <v>7060293</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,32 +4866,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598469</v>
+        <v>125598564</v>
       </c>
       <c r="B45" t="n">
-        <v>79557</v>
+        <v>91489</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528156</v>
+        <v>528199</v>
       </c>
       <c r="R45" t="n">
-        <v>7060452</v>
+        <v>7060578</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598532</v>
+        <v>125598517</v>
       </c>
       <c r="B46" t="n">
-        <v>78726</v>
+        <v>91524</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528019</v>
+        <v>528033</v>
       </c>
       <c r="R46" t="n">
-        <v>7060293</v>
+        <v>7060297</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,32 +5060,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598564</v>
+        <v>125598480</v>
       </c>
       <c r="B47" t="n">
-        <v>91489</v>
+        <v>91228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528199</v>
+        <v>528047</v>
       </c>
       <c r="R47" t="n">
-        <v>7060578</v>
+        <v>7060306</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598517</v>
+        <v>125598471</v>
       </c>
       <c r="B48" t="n">
-        <v>91524</v>
+        <v>79557</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528033</v>
+        <v>528115</v>
       </c>
       <c r="R48" t="n">
-        <v>7060297</v>
+        <v>7060370</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598480</v>
+        <v>125598469</v>
       </c>
       <c r="B49" t="n">
-        <v>91228</v>
+        <v>79557</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528047</v>
+        <v>528156</v>
       </c>
       <c r="R49" t="n">
-        <v>7060306</v>
+        <v>7060452</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125583945</v>
       </c>
       <c r="B2" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125583900</v>
       </c>
       <c r="B3" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125583874</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125584089</v>
       </c>
       <c r="B5" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125583923</v>
+        <v>125583976</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528032</v>
+        <v>527984</v>
       </c>
       <c r="R6" t="n">
-        <v>7060391</v>
+        <v>7060282</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125583976</v>
+        <v>125583923</v>
       </c>
       <c r="B7" t="n">
-        <v>78727</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527984</v>
+        <v>528032</v>
       </c>
       <c r="R7" t="n">
-        <v>7060282</v>
+        <v>7060391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>125583954</v>
       </c>
       <c r="B8" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125583966</v>
       </c>
       <c r="B9" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125583851</v>
       </c>
       <c r="B10" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125583819</v>
       </c>
       <c r="B11" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>125583910</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598443</v>
+        <v>125598549</v>
       </c>
       <c r="B13" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528204</v>
+        <v>528054</v>
       </c>
       <c r="R13" t="n">
-        <v>7060474</v>
+        <v>7060352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598569</v>
+        <v>125598443</v>
       </c>
       <c r="B14" t="n">
-        <v>92518</v>
+        <v>75067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528105</v>
+        <v>528204</v>
       </c>
       <c r="R14" t="n">
-        <v>7060384</v>
+        <v>7060474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598549</v>
+        <v>125598474</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>79561</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2048,21 +2048,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528054</v>
+        <v>528004</v>
       </c>
       <c r="R16" t="n">
-        <v>7060352</v>
+        <v>7060217</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,32 +2134,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598540</v>
+        <v>125598569</v>
       </c>
       <c r="B17" t="n">
-        <v>91389</v>
+        <v>92522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528139</v>
+        <v>528105</v>
       </c>
       <c r="R17" t="n">
-        <v>7060421</v>
+        <v>7060384</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,32 +2231,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598474</v>
+        <v>125598540</v>
       </c>
       <c r="B18" t="n">
-        <v>79557</v>
+        <v>91393</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528004</v>
+        <v>528139</v>
       </c>
       <c r="R18" t="n">
-        <v>7060217</v>
+        <v>7060421</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
         <v>125598547</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>125598568</v>
       </c>
       <c r="B20" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125598567</v>
+        <v>125598538</v>
       </c>
       <c r="B22" t="n">
-        <v>92518</v>
+        <v>91393</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528156</v>
+        <v>528219</v>
       </c>
       <c r="R22" t="n">
-        <v>7060538</v>
+        <v>7060602</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,32 +2716,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125598462</v>
+        <v>125598567</v>
       </c>
       <c r="B23" t="n">
-        <v>79586</v>
+        <v>92522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528155</v>
+        <v>528156</v>
       </c>
       <c r="R23" t="n">
-        <v>7060516</v>
+        <v>7060538</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,32 +2813,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125598538</v>
+        <v>125598578</v>
       </c>
       <c r="B24" t="n">
-        <v>91389</v>
+        <v>77921</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528219</v>
+        <v>528105</v>
       </c>
       <c r="R24" t="n">
-        <v>7060602</v>
+        <v>7060313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598578</v>
+        <v>125598462</v>
       </c>
       <c r="B25" t="n">
-        <v>77917</v>
+        <v>79590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,21 +2921,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528105</v>
+        <v>528155</v>
       </c>
       <c r="R25" t="n">
-        <v>7060313</v>
+        <v>7060516</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598530</v>
+        <v>125598478</v>
       </c>
       <c r="B26" t="n">
-        <v>78726</v>
+        <v>91232</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528109</v>
+        <v>528153</v>
       </c>
       <c r="R26" t="n">
-        <v>7060312</v>
+        <v>7060642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598573</v>
+        <v>125598513</v>
       </c>
       <c r="B27" t="n">
-        <v>92518</v>
+        <v>79979</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527916</v>
+        <v>528117</v>
       </c>
       <c r="R27" t="n">
-        <v>7060212</v>
+        <v>7060478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598513</v>
+        <v>125598530</v>
       </c>
       <c r="B28" t="n">
-        <v>79975</v>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528117</v>
+        <v>528109</v>
       </c>
       <c r="R28" t="n">
-        <v>7060478</v>
+        <v>7060312</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,32 +3298,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598478</v>
+        <v>125598573</v>
       </c>
       <c r="B29" t="n">
-        <v>91228</v>
+        <v>92522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528153</v>
+        <v>527916</v>
       </c>
       <c r="R29" t="n">
-        <v>7060642</v>
+        <v>7060212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3398,7 +3398,7 @@
         <v>125598472</v>
       </c>
       <c r="B30" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>125598533</v>
       </c>
       <c r="B31" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>125598565</v>
       </c>
       <c r="B33" t="n">
-        <v>91489</v>
+        <v>91493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,32 +3799,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598571</v>
+        <v>125598560</v>
       </c>
       <c r="B34" t="n">
-        <v>92518</v>
+        <v>82784</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527968</v>
+        <v>527902</v>
       </c>
       <c r="R34" t="n">
-        <v>7060326</v>
+        <v>7060225</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,32 +3896,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598560</v>
+        <v>125598571</v>
       </c>
       <c r="B35" t="n">
-        <v>82780</v>
+        <v>92522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527902</v>
+        <v>527968</v>
       </c>
       <c r="R35" t="n">
-        <v>7060225</v>
+        <v>7060326</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,7 +3996,7 @@
         <v>125598559</v>
       </c>
       <c r="B36" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>125598531</v>
       </c>
       <c r="B37" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598453</v>
+        <v>125598551</v>
       </c>
       <c r="B38" t="n">
-        <v>96587</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4198,21 +4198,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528210</v>
+        <v>528012</v>
       </c>
       <c r="R38" t="n">
-        <v>7060528</v>
+        <v>7060230</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598551</v>
+        <v>125598453</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>96591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528012</v>
+        <v>528210</v>
       </c>
       <c r="R39" t="n">
-        <v>7060230</v>
+        <v>7060528</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4384,7 +4384,7 @@
         <v>125598539</v>
       </c>
       <c r="B40" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598473</v>
+        <v>125598479</v>
       </c>
       <c r="B41" t="n">
-        <v>79557</v>
+        <v>91232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527959</v>
+        <v>528026</v>
       </c>
       <c r="R41" t="n">
-        <v>7060315</v>
+        <v>7060285</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4578,7 +4578,7 @@
         <v>125598552</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598479</v>
+        <v>125598473</v>
       </c>
       <c r="B43" t="n">
-        <v>91228</v>
+        <v>79561</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528026</v>
+        <v>527959</v>
       </c>
       <c r="R43" t="n">
-        <v>7060285</v>
+        <v>7060315</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4772,7 +4772,7 @@
         <v>125598532</v>
       </c>
       <c r="B44" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,32 +4866,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598564</v>
+        <v>125598471</v>
       </c>
       <c r="B45" t="n">
-        <v>91489</v>
+        <v>79561</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528199</v>
+        <v>528115</v>
       </c>
       <c r="R45" t="n">
-        <v>7060578</v>
+        <v>7060370</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598517</v>
+        <v>125598469</v>
       </c>
       <c r="B46" t="n">
-        <v>91524</v>
+        <v>79561</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528033</v>
+        <v>528156</v>
       </c>
       <c r="R46" t="n">
-        <v>7060297</v>
+        <v>7060452</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,32 +5060,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598480</v>
+        <v>125598564</v>
       </c>
       <c r="B47" t="n">
-        <v>91228</v>
+        <v>91493</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528047</v>
+        <v>528199</v>
       </c>
       <c r="R47" t="n">
-        <v>7060306</v>
+        <v>7060578</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598471</v>
+        <v>125598517</v>
       </c>
       <c r="B48" t="n">
-        <v>79557</v>
+        <v>91528</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528115</v>
+        <v>528033</v>
       </c>
       <c r="R48" t="n">
-        <v>7060370</v>
+        <v>7060297</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598469</v>
+        <v>125598480</v>
       </c>
       <c r="B49" t="n">
-        <v>79557</v>
+        <v>91232</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528156</v>
+        <v>528047</v>
       </c>
       <c r="R49" t="n">
-        <v>7060452</v>
+        <v>7060306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598463</v>
+        <v>125598558</v>
       </c>
       <c r="B50" t="n">
-        <v>79586</v>
+        <v>82784</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527988</v>
+        <v>528156</v>
       </c>
       <c r="R50" t="n">
-        <v>7060368</v>
+        <v>7060663</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598558</v>
+        <v>125598463</v>
       </c>
       <c r="B51" t="n">
-        <v>82780</v>
+        <v>79590</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528156</v>
+        <v>527988</v>
       </c>
       <c r="R51" t="n">
-        <v>7060663</v>
+        <v>7060368</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5548,7 +5548,7 @@
         <v>125598572</v>
       </c>
       <c r="B52" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>125598508</v>
       </c>
       <c r="B53" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598550</v>
+        <v>125598464</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528067</v>
+        <v>528013</v>
       </c>
       <c r="R54" t="n">
-        <v>7060280</v>
+        <v>7060176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598464</v>
+        <v>125598550</v>
       </c>
       <c r="B55" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528013</v>
+        <v>528067</v>
       </c>
       <c r="R55" t="n">
-        <v>7060176</v>
+        <v>7060280</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5936,7 +5936,7 @@
         <v>125598470</v>
       </c>
       <c r="B56" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>125598542</v>
       </c>
       <c r="B57" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>125598541</v>
       </c>
       <c r="B58" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125583976</v>
+        <v>125583923</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527984</v>
+        <v>528032</v>
       </c>
       <c r="R6" t="n">
-        <v>7060282</v>
+        <v>7060391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125583923</v>
+        <v>125583976</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528032</v>
+        <v>527984</v>
       </c>
       <c r="R7" t="n">
-        <v>7060391</v>
+        <v>7060282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1451,45 +1451,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125583851</v>
+        <v>125583819</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>92522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528097</v>
+        <v>528247</v>
       </c>
       <c r="R10" t="n">
-        <v>7060477</v>
+        <v>7060540</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,49 +1552,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125583819</v>
+        <v>125583851</v>
       </c>
       <c r="B11" t="n">
-        <v>92522</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528247</v>
+        <v>528097</v>
       </c>
       <c r="R11" t="n">
-        <v>7060540</v>
+        <v>7060477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598478</v>
+        <v>125598573</v>
       </c>
       <c r="B26" t="n">
-        <v>91232</v>
+        <v>92522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528153</v>
+        <v>527916</v>
       </c>
       <c r="R26" t="n">
-        <v>7060642</v>
+        <v>7060212</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598513</v>
+        <v>125598472</v>
       </c>
       <c r="B27" t="n">
-        <v>79979</v>
+        <v>79561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528117</v>
+        <v>528108</v>
       </c>
       <c r="R27" t="n">
-        <v>7060478</v>
+        <v>7060311</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,10 +3201,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598530</v>
+        <v>125598478</v>
       </c>
       <c r="B28" t="n">
-        <v>78730</v>
+        <v>91232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3212,21 +3212,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528109</v>
+        <v>528153</v>
       </c>
       <c r="R28" t="n">
-        <v>7060312</v>
+        <v>7060642</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598573</v>
+        <v>125598513</v>
       </c>
       <c r="B29" t="n">
-        <v>92522</v>
+        <v>79979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3309,21 +3309,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527916</v>
+        <v>528117</v>
       </c>
       <c r="R29" t="n">
-        <v>7060212</v>
+        <v>7060478</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598472</v>
+        <v>125598530</v>
       </c>
       <c r="B30" t="n">
-        <v>79561</v>
+        <v>78730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528108</v>
+        <v>528109</v>
       </c>
       <c r="R30" t="n">
-        <v>7060311</v>
+        <v>7060312</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598532</v>
+        <v>125598471</v>
       </c>
       <c r="B44" t="n">
-        <v>78730</v>
+        <v>79561</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528019</v>
+        <v>528115</v>
       </c>
       <c r="R44" t="n">
-        <v>7060293</v>
+        <v>7060370</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598471</v>
+        <v>125598469</v>
       </c>
       <c r="B45" t="n">
         <v>79561</v>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528115</v>
+        <v>528156</v>
       </c>
       <c r="R45" t="n">
-        <v>7060370</v>
+        <v>7060452</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598469</v>
+        <v>125598564</v>
       </c>
       <c r="B46" t="n">
-        <v>79561</v>
+        <v>91493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528156</v>
+        <v>528199</v>
       </c>
       <c r="R46" t="n">
-        <v>7060452</v>
+        <v>7060578</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,32 +5060,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598564</v>
+        <v>125598517</v>
       </c>
       <c r="B47" t="n">
-        <v>91493</v>
+        <v>91528</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528199</v>
+        <v>528033</v>
       </c>
       <c r="R47" t="n">
-        <v>7060578</v>
+        <v>7060297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598517</v>
+        <v>125598480</v>
       </c>
       <c r="B48" t="n">
-        <v>91528</v>
+        <v>91232</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528033</v>
+        <v>528047</v>
       </c>
       <c r="R48" t="n">
-        <v>7060297</v>
+        <v>7060306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598480</v>
+        <v>125598532</v>
       </c>
       <c r="B49" t="n">
-        <v>91232</v>
+        <v>78730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528047</v>
+        <v>528019</v>
       </c>
       <c r="R49" t="n">
-        <v>7060306</v>
+        <v>7060293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -1451,49 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125583819</v>
+        <v>125583851</v>
       </c>
       <c r="B10" t="n">
-        <v>92522</v>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528247</v>
+        <v>528097</v>
       </c>
       <c r="R10" t="n">
-        <v>7060540</v>
+        <v>7060477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,45 +1548,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125583851</v>
+        <v>125583819</v>
       </c>
       <c r="B11" t="n">
-        <v>78730</v>
+        <v>92522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528097</v>
+        <v>528247</v>
       </c>
       <c r="R11" t="n">
-        <v>7060477</v>
+        <v>7060540</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598549</v>
+        <v>125598474</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528054</v>
+        <v>528004</v>
       </c>
       <c r="R13" t="n">
-        <v>7060352</v>
+        <v>7060217</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598443</v>
+        <v>125598540</v>
       </c>
       <c r="B14" t="n">
-        <v>75067</v>
+        <v>91393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528204</v>
+        <v>528139</v>
       </c>
       <c r="R14" t="n">
-        <v>7060474</v>
+        <v>7060421</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598442</v>
+        <v>125598443</v>
       </c>
       <c r="B15" t="n">
         <v>75067</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528139</v>
+        <v>528204</v>
       </c>
       <c r="R15" t="n">
-        <v>7060573</v>
+        <v>7060474</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,32 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598474</v>
+        <v>125598569</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>92522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528004</v>
+        <v>528105</v>
       </c>
       <c r="R16" t="n">
-        <v>7060217</v>
+        <v>7060384</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,32 +2134,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598569</v>
+        <v>125598442</v>
       </c>
       <c r="B17" t="n">
-        <v>92522</v>
+        <v>75067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528105</v>
+        <v>528139</v>
       </c>
       <c r="R17" t="n">
-        <v>7060384</v>
+        <v>7060573</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,32 +2231,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598540</v>
+        <v>125598549</v>
       </c>
       <c r="B18" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528139</v>
+        <v>528054</v>
       </c>
       <c r="R18" t="n">
-        <v>7060421</v>
+        <v>7060352</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125598578</v>
+        <v>125598462</v>
       </c>
       <c r="B24" t="n">
-        <v>77921</v>
+        <v>79590</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528105</v>
+        <v>528155</v>
       </c>
       <c r="R24" t="n">
-        <v>7060313</v>
+        <v>7060516</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598462</v>
+        <v>125598578</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>77921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,21 +2921,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528155</v>
+        <v>528105</v>
       </c>
       <c r="R25" t="n">
-        <v>7060516</v>
+        <v>7060313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598573</v>
+        <v>125598472</v>
       </c>
       <c r="B26" t="n">
-        <v>92522</v>
+        <v>79561</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527916</v>
+        <v>528108</v>
       </c>
       <c r="R26" t="n">
-        <v>7060212</v>
+        <v>7060311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598472</v>
+        <v>125598478</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>91232</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528108</v>
+        <v>528153</v>
       </c>
       <c r="R27" t="n">
-        <v>7060311</v>
+        <v>7060642</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,10 +3201,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598478</v>
+        <v>125598530</v>
       </c>
       <c r="B28" t="n">
-        <v>91232</v>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3212,21 +3212,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528153</v>
+        <v>528109</v>
       </c>
       <c r="R28" t="n">
-        <v>7060642</v>
+        <v>7060312</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598513</v>
+        <v>125598573</v>
       </c>
       <c r="B29" t="n">
-        <v>79979</v>
+        <v>92522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3309,21 +3309,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528117</v>
+        <v>527916</v>
       </c>
       <c r="R29" t="n">
-        <v>7060478</v>
+        <v>7060212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,32 +3395,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598530</v>
+        <v>125598513</v>
       </c>
       <c r="B30" t="n">
-        <v>78730</v>
+        <v>79979</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528109</v>
+        <v>528117</v>
       </c>
       <c r="R30" t="n">
-        <v>7060312</v>
+        <v>7060478</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3799,32 +3799,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598560</v>
+        <v>125598571</v>
       </c>
       <c r="B34" t="n">
-        <v>82784</v>
+        <v>92522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527902</v>
+        <v>527968</v>
       </c>
       <c r="R34" t="n">
-        <v>7060225</v>
+        <v>7060326</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,32 +3896,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598571</v>
+        <v>125598560</v>
       </c>
       <c r="B35" t="n">
-        <v>92522</v>
+        <v>82784</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527968</v>
+        <v>527902</v>
       </c>
       <c r="R35" t="n">
-        <v>7060326</v>
+        <v>7060225</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598551</v>
+        <v>125598453</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>96592</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4198,21 +4198,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528012</v>
+        <v>528210</v>
       </c>
       <c r="R38" t="n">
-        <v>7060230</v>
+        <v>7060528</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598453</v>
+        <v>125598551</v>
       </c>
       <c r="B39" t="n">
-        <v>96591</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528210</v>
+        <v>528012</v>
       </c>
       <c r="R39" t="n">
-        <v>7060528</v>
+        <v>7060230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598479</v>
+        <v>125598473</v>
       </c>
       <c r="B41" t="n">
-        <v>91232</v>
+        <v>79561</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528026</v>
+        <v>527959</v>
       </c>
       <c r="R41" t="n">
-        <v>7060285</v>
+        <v>7060315</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598552</v>
+        <v>125598479</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527891</v>
+        <v>528026</v>
       </c>
       <c r="R42" t="n">
-        <v>7060221</v>
+        <v>7060285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598473</v>
+        <v>125598552</v>
       </c>
       <c r="B43" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527959</v>
+        <v>527891</v>
       </c>
       <c r="R43" t="n">
-        <v>7060315</v>
+        <v>7060221</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598464</v>
+        <v>125598470</v>
       </c>
       <c r="B54" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528013</v>
+        <v>528137</v>
       </c>
       <c r="R54" t="n">
-        <v>7060176</v>
+        <v>7060400</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598470</v>
+        <v>125598464</v>
       </c>
       <c r="B56" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5944,21 +5944,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528137</v>
+        <v>528013</v>
       </c>
       <c r="R56" t="n">
-        <v>7060400</v>
+        <v>7060176</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598540</v>
+        <v>125598443</v>
       </c>
       <c r="B14" t="n">
-        <v>91393</v>
+        <v>75067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528139</v>
+        <v>528204</v>
       </c>
       <c r="R14" t="n">
-        <v>7060421</v>
+        <v>7060474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598443</v>
+        <v>125598569</v>
       </c>
       <c r="B15" t="n">
-        <v>75067</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528204</v>
+        <v>528105</v>
       </c>
       <c r="R15" t="n">
-        <v>7060474</v>
+        <v>7060384</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,32 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598569</v>
+        <v>125598540</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>91393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528105</v>
+        <v>528139</v>
       </c>
       <c r="R16" t="n">
-        <v>7060384</v>
+        <v>7060421</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B31" t="n">
-        <v>78730</v>
+        <v>57811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,34 +3503,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R31" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B32" t="n">
-        <v>57811</v>
+        <v>78730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3600,50 +3616,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R32" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598473</v>
+        <v>125598479</v>
       </c>
       <c r="B41" t="n">
-        <v>79561</v>
+        <v>91232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527959</v>
+        <v>528026</v>
       </c>
       <c r="R41" t="n">
-        <v>7060315</v>
+        <v>7060285</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598479</v>
+        <v>125598473</v>
       </c>
       <c r="B42" t="n">
-        <v>91232</v>
+        <v>79561</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528026</v>
+        <v>527959</v>
       </c>
       <c r="R42" t="n">
-        <v>7060285</v>
+        <v>7060315</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125583923</v>
+        <v>125583976</v>
       </c>
       <c r="B6" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528032</v>
+        <v>527984</v>
       </c>
       <c r="R6" t="n">
-        <v>7060391</v>
+        <v>7060282</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125583976</v>
+        <v>125583923</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527984</v>
+        <v>528032</v>
       </c>
       <c r="R7" t="n">
-        <v>7060282</v>
+        <v>7060391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598479</v>
+        <v>125598473</v>
       </c>
       <c r="B41" t="n">
-        <v>91232</v>
+        <v>79561</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528026</v>
+        <v>527959</v>
       </c>
       <c r="R41" t="n">
-        <v>7060285</v>
+        <v>7060315</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598473</v>
+        <v>125598479</v>
       </c>
       <c r="B42" t="n">
-        <v>79561</v>
+        <v>91232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527959</v>
+        <v>528026</v>
       </c>
       <c r="R42" t="n">
-        <v>7060315</v>
+        <v>7060285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598471</v>
+        <v>125598532</v>
       </c>
       <c r="B44" t="n">
-        <v>79561</v>
+        <v>78730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528115</v>
+        <v>528019</v>
       </c>
       <c r="R44" t="n">
-        <v>7060370</v>
+        <v>7060293</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,32 +4866,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598469</v>
+        <v>125598564</v>
       </c>
       <c r="B45" t="n">
-        <v>79561</v>
+        <v>91493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528156</v>
+        <v>528199</v>
       </c>
       <c r="R45" t="n">
-        <v>7060452</v>
+        <v>7060578</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598564</v>
+        <v>125598517</v>
       </c>
       <c r="B46" t="n">
-        <v>91493</v>
+        <v>91528</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528199</v>
+        <v>528033</v>
       </c>
       <c r="R46" t="n">
-        <v>7060578</v>
+        <v>7060297</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598517</v>
+        <v>125598480</v>
       </c>
       <c r="B47" t="n">
-        <v>91528</v>
+        <v>91232</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528033</v>
+        <v>528047</v>
       </c>
       <c r="R47" t="n">
-        <v>7060297</v>
+        <v>7060306</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598480</v>
+        <v>125598471</v>
       </c>
       <c r="B48" t="n">
-        <v>91232</v>
+        <v>79561</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528047</v>
+        <v>528115</v>
       </c>
       <c r="R48" t="n">
-        <v>7060306</v>
+        <v>7060370</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598532</v>
+        <v>125598469</v>
       </c>
       <c r="B49" t="n">
-        <v>78730</v>
+        <v>79561</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528019</v>
+        <v>528156</v>
       </c>
       <c r="R49" t="n">
-        <v>7060293</v>
+        <v>7060452</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125583945</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125583900</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125583874</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125584089</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125583976</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125583923</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125583954</v>
       </c>
       <c r="B8" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125583966</v>
       </c>
       <c r="B9" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125583851</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125583819</v>
       </c>
       <c r="B11" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>125583910</v>
       </c>
       <c r="B12" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,32 +1746,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598474</v>
+        <v>125598540</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>91395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528004</v>
+        <v>528139</v>
       </c>
       <c r="R13" t="n">
-        <v>7060217</v>
+        <v>7060421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,7 +1846,7 @@
         <v>125598443</v>
       </c>
       <c r="B14" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>125598569</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,32 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598540</v>
+        <v>125598442</v>
       </c>
       <c r="B16" t="n">
-        <v>91393</v>
+        <v>75068</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
         <v>528139</v>
       </c>
       <c r="R16" t="n">
-        <v>7060421</v>
+        <v>7060573</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598442</v>
+        <v>125598549</v>
       </c>
       <c r="B17" t="n">
-        <v>75067</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528139</v>
+        <v>528054</v>
       </c>
       <c r="R17" t="n">
-        <v>7060573</v>
+        <v>7060352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598549</v>
+        <v>125598474</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>79562</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528054</v>
+        <v>528004</v>
       </c>
       <c r="R18" t="n">
-        <v>7060352</v>
+        <v>7060217</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
         <v>125598547</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>125598568</v>
       </c>
       <c r="B20" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>125598445</v>
       </c>
       <c r="B21" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,32 +2619,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125598538</v>
+        <v>125598578</v>
       </c>
       <c r="B22" t="n">
-        <v>91393</v>
+        <v>77922</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528219</v>
+        <v>528105</v>
       </c>
       <c r="R22" t="n">
-        <v>7060602</v>
+        <v>7060313</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,32 +2716,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125598567</v>
+        <v>125598538</v>
       </c>
       <c r="B23" t="n">
-        <v>92522</v>
+        <v>91395</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528156</v>
+        <v>528219</v>
       </c>
       <c r="R23" t="n">
-        <v>7060538</v>
+        <v>7060602</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,32 +2813,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125598462</v>
+        <v>125598567</v>
       </c>
       <c r="B24" t="n">
-        <v>79590</v>
+        <v>92524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528155</v>
+        <v>528156</v>
       </c>
       <c r="R24" t="n">
-        <v>7060516</v>
+        <v>7060538</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598578</v>
+        <v>125598462</v>
       </c>
       <c r="B25" t="n">
-        <v>77921</v>
+        <v>79591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,21 +2921,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528105</v>
+        <v>528155</v>
       </c>
       <c r="R25" t="n">
-        <v>7060313</v>
+        <v>7060516</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598472</v>
+        <v>125598478</v>
       </c>
       <c r="B26" t="n">
-        <v>79561</v>
+        <v>91234</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528108</v>
+        <v>528153</v>
       </c>
       <c r="R26" t="n">
-        <v>7060311</v>
+        <v>7060642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598478</v>
+        <v>125598530</v>
       </c>
       <c r="B27" t="n">
-        <v>91232</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528153</v>
+        <v>528109</v>
       </c>
       <c r="R27" t="n">
-        <v>7060642</v>
+        <v>7060312</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598530</v>
+        <v>125598573</v>
       </c>
       <c r="B28" t="n">
-        <v>78730</v>
+        <v>92524</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528109</v>
+        <v>527916</v>
       </c>
       <c r="R28" t="n">
-        <v>7060312</v>
+        <v>7060212</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598573</v>
+        <v>125598513</v>
       </c>
       <c r="B29" t="n">
-        <v>92522</v>
+        <v>79980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3309,21 +3309,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527916</v>
+        <v>528117</v>
       </c>
       <c r="R29" t="n">
-        <v>7060212</v>
+        <v>7060478</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,32 +3395,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598513</v>
+        <v>125598472</v>
       </c>
       <c r="B30" t="n">
-        <v>79979</v>
+        <v>79562</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528117</v>
+        <v>528108</v>
       </c>
       <c r="R30" t="n">
-        <v>7060478</v>
+        <v>7060311</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B31" t="n">
-        <v>57811</v>
+        <v>78731</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,50 +3503,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R31" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3589,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B32" t="n">
-        <v>78730</v>
+        <v>57812</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,34 +3600,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R32" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3705,7 +3705,7 @@
         <v>125598565</v>
       </c>
       <c r="B33" t="n">
-        <v>91493</v>
+        <v>91495</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,32 +3799,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598571</v>
+        <v>125598560</v>
       </c>
       <c r="B34" t="n">
-        <v>92522</v>
+        <v>82785</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527968</v>
+        <v>527902</v>
       </c>
       <c r="R34" t="n">
-        <v>7060326</v>
+        <v>7060225</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,32 +3896,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598560</v>
+        <v>125598571</v>
       </c>
       <c r="B35" t="n">
-        <v>82784</v>
+        <v>92524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527902</v>
+        <v>527968</v>
       </c>
       <c r="R35" t="n">
-        <v>7060225</v>
+        <v>7060326</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,10 +3993,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598559</v>
+        <v>125598531</v>
       </c>
       <c r="B36" t="n">
-        <v>82784</v>
+        <v>78731</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4004,21 +4004,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528154</v>
+        <v>527988</v>
       </c>
       <c r="R36" t="n">
-        <v>7060576</v>
+        <v>7060369</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,10 +4090,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598531</v>
+        <v>125598559</v>
       </c>
       <c r="B37" t="n">
-        <v>78730</v>
+        <v>82785</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4101,21 +4101,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527988</v>
+        <v>528154</v>
       </c>
       <c r="R37" t="n">
-        <v>7060369</v>
+        <v>7060576</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
         <v>125598453</v>
       </c>
       <c r="B38" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>125598551</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>125598539</v>
       </c>
       <c r="B40" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598473</v>
+        <v>125598479</v>
       </c>
       <c r="B41" t="n">
-        <v>79561</v>
+        <v>91234</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527959</v>
+        <v>528026</v>
       </c>
       <c r="R41" t="n">
-        <v>7060315</v>
+        <v>7060285</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598479</v>
+        <v>125598552</v>
       </c>
       <c r="B42" t="n">
-        <v>91232</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528026</v>
+        <v>527891</v>
       </c>
       <c r="R42" t="n">
-        <v>7060285</v>
+        <v>7060221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598552</v>
+        <v>125598473</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>79562</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527891</v>
+        <v>527959</v>
       </c>
       <c r="R43" t="n">
-        <v>7060221</v>
+        <v>7060315</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598532</v>
+        <v>125598517</v>
       </c>
       <c r="B44" t="n">
-        <v>78730</v>
+        <v>91530</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528019</v>
+        <v>528033</v>
       </c>
       <c r="R44" t="n">
-        <v>7060293</v>
+        <v>7060297</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,32 +4866,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598564</v>
+        <v>125598471</v>
       </c>
       <c r="B45" t="n">
-        <v>91493</v>
+        <v>79562</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528199</v>
+        <v>528115</v>
       </c>
       <c r="R45" t="n">
-        <v>7060578</v>
+        <v>7060370</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598517</v>
+        <v>125598469</v>
       </c>
       <c r="B46" t="n">
-        <v>91528</v>
+        <v>79562</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528033</v>
+        <v>528156</v>
       </c>
       <c r="R46" t="n">
-        <v>7060297</v>
+        <v>7060452</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,32 +5060,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598480</v>
+        <v>125598564</v>
       </c>
       <c r="B47" t="n">
-        <v>91232</v>
+        <v>91495</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528047</v>
+        <v>528199</v>
       </c>
       <c r="R47" t="n">
-        <v>7060306</v>
+        <v>7060578</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598471</v>
+        <v>125598480</v>
       </c>
       <c r="B48" t="n">
-        <v>79561</v>
+        <v>91234</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528115</v>
+        <v>528047</v>
       </c>
       <c r="R48" t="n">
-        <v>7060370</v>
+        <v>7060306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598469</v>
+        <v>125598532</v>
       </c>
       <c r="B49" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528156</v>
+        <v>528019</v>
       </c>
       <c r="R49" t="n">
-        <v>7060452</v>
+        <v>7060293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5354,7 +5354,7 @@
         <v>125598558</v>
       </c>
       <c r="B50" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125598463</v>
       </c>
       <c r="B51" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>125598572</v>
       </c>
       <c r="B52" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>125598508</v>
       </c>
       <c r="B53" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598470</v>
+        <v>125598550</v>
       </c>
       <c r="B54" t="n">
-        <v>79561</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528137</v>
+        <v>528067</v>
       </c>
       <c r="R54" t="n">
-        <v>7060400</v>
+        <v>7060280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598550</v>
+        <v>125598464</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528067</v>
+        <v>528013</v>
       </c>
       <c r="R55" t="n">
-        <v>7060280</v>
+        <v>7060176</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598464</v>
+        <v>125598470</v>
       </c>
       <c r="B56" t="n">
-        <v>79590</v>
+        <v>79562</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5944,21 +5944,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528013</v>
+        <v>528137</v>
       </c>
       <c r="R56" t="n">
-        <v>7060176</v>
+        <v>7060400</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6030,10 +6030,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598542</v>
+        <v>125598541</v>
       </c>
       <c r="B57" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527984</v>
+        <v>528123</v>
       </c>
       <c r="R57" t="n">
-        <v>7060358</v>
+        <v>7060390</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598541</v>
+        <v>125598542</v>
       </c>
       <c r="B58" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528123</v>
+        <v>527984</v>
       </c>
       <c r="R58" t="n">
-        <v>7060390</v>
+        <v>7060358</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6227,7 +6227,7 @@
         <v>125598485</v>
       </c>
       <c r="B59" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>125598483</v>
       </c>
       <c r="B60" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>125598484</v>
       </c>
       <c r="B61" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -4769,32 +4769,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598517</v>
+        <v>125598564</v>
       </c>
       <c r="B44" t="n">
-        <v>91530</v>
+        <v>91495</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528033</v>
+        <v>528199</v>
       </c>
       <c r="R44" t="n">
-        <v>7060297</v>
+        <v>7060578</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598471</v>
+        <v>125598480</v>
       </c>
       <c r="B45" t="n">
-        <v>79562</v>
+        <v>91234</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528115</v>
+        <v>528047</v>
       </c>
       <c r="R45" t="n">
-        <v>7060370</v>
+        <v>7060306</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598469</v>
+        <v>125598532</v>
       </c>
       <c r="B46" t="n">
-        <v>79562</v>
+        <v>78731</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528156</v>
+        <v>528019</v>
       </c>
       <c r="R46" t="n">
-        <v>7060452</v>
+        <v>7060293</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,32 +5060,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598564</v>
+        <v>125598517</v>
       </c>
       <c r="B47" t="n">
-        <v>91495</v>
+        <v>91530</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528199</v>
+        <v>528033</v>
       </c>
       <c r="R47" t="n">
-        <v>7060578</v>
+        <v>7060297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598480</v>
+        <v>125598471</v>
       </c>
       <c r="B48" t="n">
-        <v>91234</v>
+        <v>79562</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528047</v>
+        <v>528115</v>
       </c>
       <c r="R48" t="n">
-        <v>7060306</v>
+        <v>7060370</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598532</v>
+        <v>125598469</v>
       </c>
       <c r="B49" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528019</v>
+        <v>528156</v>
       </c>
       <c r="R49" t="n">
-        <v>7060293</v>
+        <v>7060452</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598558</v>
+        <v>125598463</v>
       </c>
       <c r="B50" t="n">
-        <v>82785</v>
+        <v>79591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528156</v>
+        <v>527988</v>
       </c>
       <c r="R50" t="n">
-        <v>7060663</v>
+        <v>7060368</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598463</v>
+        <v>125598558</v>
       </c>
       <c r="B51" t="n">
-        <v>79591</v>
+        <v>82785</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527988</v>
+        <v>528156</v>
       </c>
       <c r="R51" t="n">
-        <v>7060368</v>
+        <v>7060663</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>125583954</v>
       </c>
       <c r="B8" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125583819</v>
       </c>
       <c r="B11" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,32 +1746,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598540</v>
+        <v>125598443</v>
       </c>
       <c r="B13" t="n">
-        <v>91395</v>
+        <v>75068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528139</v>
+        <v>528204</v>
       </c>
       <c r="R13" t="n">
-        <v>7060421</v>
+        <v>7060474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598443</v>
+        <v>125598569</v>
       </c>
       <c r="B14" t="n">
-        <v>75068</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528204</v>
+        <v>528105</v>
       </c>
       <c r="R14" t="n">
-        <v>7060474</v>
+        <v>7060384</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598569</v>
+        <v>125598442</v>
       </c>
       <c r="B15" t="n">
-        <v>92524</v>
+        <v>75068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528105</v>
+        <v>528139</v>
       </c>
       <c r="R15" t="n">
-        <v>7060384</v>
+        <v>7060573</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,32 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598442</v>
+        <v>125598540</v>
       </c>
       <c r="B16" t="n">
-        <v>75068</v>
+        <v>91397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
         <v>528139</v>
       </c>
       <c r="R16" t="n">
-        <v>7060573</v>
+        <v>7060421</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2428,7 +2428,7 @@
         <v>125598568</v>
       </c>
       <c r="B20" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>125598538</v>
       </c>
       <c r="B23" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>125598567</v>
       </c>
       <c r="B24" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598478</v>
+        <v>125598472</v>
       </c>
       <c r="B26" t="n">
-        <v>91234</v>
+        <v>79562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528153</v>
+        <v>528108</v>
       </c>
       <c r="R26" t="n">
-        <v>7060642</v>
+        <v>7060311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
         <v>125598573</v>
       </c>
       <c r="B28" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598472</v>
+        <v>125598478</v>
       </c>
       <c r="B30" t="n">
-        <v>79562</v>
+        <v>91236</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528108</v>
+        <v>528153</v>
       </c>
       <c r="R30" t="n">
-        <v>7060311</v>
+        <v>7060642</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B31" t="n">
-        <v>78731</v>
+        <v>57812</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,34 +3503,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R31" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B32" t="n">
-        <v>57812</v>
+        <v>78731</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3600,50 +3616,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R32" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3705,7 +3705,7 @@
         <v>125598565</v>
       </c>
       <c r="B33" t="n">
-        <v>91495</v>
+        <v>91497</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>125598571</v>
       </c>
       <c r="B35" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>125598453</v>
       </c>
       <c r="B38" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>125598539</v>
       </c>
       <c r="B40" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>125598479</v>
       </c>
       <c r="B41" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>125598564</v>
       </c>
       <c r="B44" t="n">
-        <v>91495</v>
+        <v>91497</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598480</v>
+        <v>125598517</v>
       </c>
       <c r="B45" t="n">
-        <v>91234</v>
+        <v>91532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528047</v>
+        <v>528033</v>
       </c>
       <c r="R45" t="n">
-        <v>7060306</v>
+        <v>7060297</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598532</v>
+        <v>125598480</v>
       </c>
       <c r="B46" t="n">
-        <v>78731</v>
+        <v>91236</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528019</v>
+        <v>528047</v>
       </c>
       <c r="R46" t="n">
-        <v>7060293</v>
+        <v>7060306</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598517</v>
+        <v>125598532</v>
       </c>
       <c r="B47" t="n">
-        <v>91530</v>
+        <v>78731</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528033</v>
+        <v>528019</v>
       </c>
       <c r="R47" t="n">
-        <v>7060297</v>
+        <v>7060293</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598463</v>
+        <v>125598558</v>
       </c>
       <c r="B50" t="n">
-        <v>79591</v>
+        <v>82785</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527988</v>
+        <v>528156</v>
       </c>
       <c r="R50" t="n">
-        <v>7060368</v>
+        <v>7060663</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598558</v>
+        <v>125598463</v>
       </c>
       <c r="B51" t="n">
-        <v>82785</v>
+        <v>79591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528156</v>
+        <v>527988</v>
       </c>
       <c r="R51" t="n">
-        <v>7060663</v>
+        <v>7060368</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5548,7 +5548,7 @@
         <v>125598572</v>
       </c>
       <c r="B52" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6030,10 +6030,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598541</v>
+        <v>125598542</v>
       </c>
       <c r="B57" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528123</v>
+        <v>527984</v>
       </c>
       <c r="R57" t="n">
-        <v>7060390</v>
+        <v>7060358</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598542</v>
+        <v>125598541</v>
       </c>
       <c r="B58" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527984</v>
+        <v>528123</v>
       </c>
       <c r="R58" t="n">
-        <v>7060358</v>
+        <v>7060390</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598517</v>
+        <v>125598471</v>
       </c>
       <c r="B45" t="n">
-        <v>91532</v>
+        <v>79562</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528033</v>
+        <v>528115</v>
       </c>
       <c r="R45" t="n">
-        <v>7060297</v>
+        <v>7060370</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598480</v>
+        <v>125598469</v>
       </c>
       <c r="B46" t="n">
-        <v>91236</v>
+        <v>79562</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528047</v>
+        <v>528156</v>
       </c>
       <c r="R46" t="n">
-        <v>7060306</v>
+        <v>7060452</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598532</v>
+        <v>125598517</v>
       </c>
       <c r="B47" t="n">
-        <v>78731</v>
+        <v>91532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528019</v>
+        <v>528033</v>
       </c>
       <c r="R47" t="n">
-        <v>7060293</v>
+        <v>7060297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598471</v>
+        <v>125598480</v>
       </c>
       <c r="B48" t="n">
-        <v>79562</v>
+        <v>91236</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528115</v>
+        <v>528047</v>
       </c>
       <c r="R48" t="n">
-        <v>7060370</v>
+        <v>7060306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598469</v>
+        <v>125598532</v>
       </c>
       <c r="B49" t="n">
-        <v>79562</v>
+        <v>78731</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528156</v>
+        <v>528019</v>
       </c>
       <c r="R49" t="n">
-        <v>7060452</v>
+        <v>7060293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125583976</v>
+        <v>125583923</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527984</v>
+        <v>528032</v>
       </c>
       <c r="R6" t="n">
-        <v>7060282</v>
+        <v>7060391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125583923</v>
+        <v>125583976</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528032</v>
+        <v>527984</v>
       </c>
       <c r="R7" t="n">
-        <v>7060391</v>
+        <v>7060282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>125583954</v>
       </c>
       <c r="B8" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125583819</v>
       </c>
       <c r="B11" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598569</v>
+        <v>125598442</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>75068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528105</v>
+        <v>528139</v>
       </c>
       <c r="R14" t="n">
-        <v>7060384</v>
+        <v>7060573</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598442</v>
+        <v>125598549</v>
       </c>
       <c r="B15" t="n">
-        <v>75068</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1951,21 +1951,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528139</v>
+        <v>528054</v>
       </c>
       <c r="R15" t="n">
-        <v>7060573</v>
+        <v>7060352</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,7 +2040,7 @@
         <v>125598540</v>
       </c>
       <c r="B16" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,32 +2134,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598549</v>
+        <v>125598569</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528054</v>
+        <v>528105</v>
       </c>
       <c r="R17" t="n">
-        <v>7060352</v>
+        <v>7060384</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,7 +2428,7 @@
         <v>125598568</v>
       </c>
       <c r="B20" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,32 +2716,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125598538</v>
+        <v>125598462</v>
       </c>
       <c r="B23" t="n">
-        <v>91397</v>
+        <v>79591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528219</v>
+        <v>528155</v>
       </c>
       <c r="R23" t="n">
-        <v>7060602</v>
+        <v>7060516</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
         <v>125598567</v>
       </c>
       <c r="B24" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,32 +2910,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598462</v>
+        <v>125598538</v>
       </c>
       <c r="B25" t="n">
-        <v>79591</v>
+        <v>91399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528155</v>
+        <v>528219</v>
       </c>
       <c r="R25" t="n">
-        <v>7060516</v>
+        <v>7060602</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598472</v>
+        <v>125598530</v>
       </c>
       <c r="B26" t="n">
-        <v>79562</v>
+        <v>78731</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528108</v>
+        <v>528109</v>
       </c>
       <c r="R26" t="n">
-        <v>7060311</v>
+        <v>7060312</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598530</v>
+        <v>125598513</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>79980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528109</v>
+        <v>528117</v>
       </c>
       <c r="R27" t="n">
-        <v>7060312</v>
+        <v>7060478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598573</v>
+        <v>125598472</v>
       </c>
       <c r="B28" t="n">
-        <v>92526</v>
+        <v>79562</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527916</v>
+        <v>528108</v>
       </c>
       <c r="R28" t="n">
-        <v>7060212</v>
+        <v>7060311</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598513</v>
+        <v>125598573</v>
       </c>
       <c r="B29" t="n">
-        <v>79980</v>
+        <v>92528</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3309,21 +3309,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528117</v>
+        <v>527916</v>
       </c>
       <c r="R29" t="n">
-        <v>7060478</v>
+        <v>7060212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3398,7 +3398,7 @@
         <v>125598478</v>
       </c>
       <c r="B30" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598506</v>
+        <v>125598533</v>
       </c>
       <c r="B31" t="n">
-        <v>57812</v>
+        <v>78731</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,50 +3503,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528169</v>
+        <v>527893</v>
       </c>
       <c r="R31" t="n">
-        <v>7060483</v>
+        <v>7060200</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3589,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598533</v>
+        <v>125598506</v>
       </c>
       <c r="B32" t="n">
-        <v>78731</v>
+        <v>57812</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,34 +3600,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527893</v>
+        <v>528169</v>
       </c>
       <c r="R32" t="n">
-        <v>7060200</v>
+        <v>7060483</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3705,7 +3705,7 @@
         <v>125598565</v>
       </c>
       <c r="B33" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>125598571</v>
       </c>
       <c r="B35" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598453</v>
+        <v>125598551</v>
       </c>
       <c r="B38" t="n">
-        <v>96596</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4198,21 +4198,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528210</v>
+        <v>528012</v>
       </c>
       <c r="R38" t="n">
-        <v>7060528</v>
+        <v>7060230</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598551</v>
+        <v>125598453</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>96598</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528012</v>
+        <v>528210</v>
       </c>
       <c r="R39" t="n">
-        <v>7060230</v>
+        <v>7060528</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4384,7 +4384,7 @@
         <v>125598539</v>
       </c>
       <c r="B40" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598479</v>
+        <v>125598473</v>
       </c>
       <c r="B41" t="n">
-        <v>91236</v>
+        <v>79562</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528026</v>
+        <v>527959</v>
       </c>
       <c r="R41" t="n">
-        <v>7060285</v>
+        <v>7060315</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598473</v>
+        <v>125598479</v>
       </c>
       <c r="B43" t="n">
-        <v>79562</v>
+        <v>91238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527959</v>
+        <v>528026</v>
       </c>
       <c r="R43" t="n">
-        <v>7060315</v>
+        <v>7060285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,32 +4769,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598564</v>
+        <v>125598532</v>
       </c>
       <c r="B44" t="n">
-        <v>91497</v>
+        <v>78731</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528199</v>
+        <v>528019</v>
       </c>
       <c r="R44" t="n">
-        <v>7060578</v>
+        <v>7060293</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598471</v>
+        <v>125598517</v>
       </c>
       <c r="B45" t="n">
-        <v>79562</v>
+        <v>91534</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528115</v>
+        <v>528033</v>
       </c>
       <c r="R45" t="n">
-        <v>7060370</v>
+        <v>7060297</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,32 +4963,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598469</v>
+        <v>125598564</v>
       </c>
       <c r="B46" t="n">
-        <v>79562</v>
+        <v>91499</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528156</v>
+        <v>528199</v>
       </c>
       <c r="R46" t="n">
-        <v>7060452</v>
+        <v>7060578</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598517</v>
+        <v>125598480</v>
       </c>
       <c r="B47" t="n">
-        <v>91532</v>
+        <v>91238</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528033</v>
+        <v>528047</v>
       </c>
       <c r="R47" t="n">
-        <v>7060297</v>
+        <v>7060306</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598480</v>
+        <v>125598471</v>
       </c>
       <c r="B48" t="n">
-        <v>91236</v>
+        <v>79562</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528047</v>
+        <v>528115</v>
       </c>
       <c r="R48" t="n">
-        <v>7060306</v>
+        <v>7060370</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598532</v>
+        <v>125598469</v>
       </c>
       <c r="B49" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528019</v>
+        <v>528156</v>
       </c>
       <c r="R49" t="n">
-        <v>7060293</v>
+        <v>7060452</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598558</v>
+        <v>125598463</v>
       </c>
       <c r="B50" t="n">
-        <v>82785</v>
+        <v>79591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528156</v>
+        <v>527988</v>
       </c>
       <c r="R50" t="n">
-        <v>7060663</v>
+        <v>7060368</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598463</v>
+        <v>125598558</v>
       </c>
       <c r="B51" t="n">
-        <v>79591</v>
+        <v>82785</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527988</v>
+        <v>528156</v>
       </c>
       <c r="R51" t="n">
-        <v>7060368</v>
+        <v>7060663</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5548,7 +5548,7 @@
         <v>125598572</v>
       </c>
       <c r="B52" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6030,10 +6030,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598542</v>
+        <v>125598541</v>
       </c>
       <c r="B57" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527984</v>
+        <v>528123</v>
       </c>
       <c r="R57" t="n">
-        <v>7060358</v>
+        <v>7060390</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598541</v>
+        <v>125598542</v>
       </c>
       <c r="B58" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528123</v>
+        <v>527984</v>
       </c>
       <c r="R58" t="n">
-        <v>7060390</v>
+        <v>7060358</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -4187,10 +4187,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598551</v>
+        <v>125598453</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>96598</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4198,21 +4198,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528012</v>
+        <v>528210</v>
       </c>
       <c r="R38" t="n">
-        <v>7060230</v>
+        <v>7060528</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598453</v>
+        <v>125598551</v>
       </c>
       <c r="B39" t="n">
-        <v>96598</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528210</v>
+        <v>528012</v>
       </c>
       <c r="R39" t="n">
-        <v>7060528</v>
+        <v>7060230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598473</v>
+        <v>125598552</v>
       </c>
       <c r="B41" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527959</v>
+        <v>527891</v>
       </c>
       <c r="R41" t="n">
-        <v>7060315</v>
+        <v>7060221</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598552</v>
+        <v>125598473</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527891</v>
+        <v>527959</v>
       </c>
       <c r="R42" t="n">
-        <v>7060221</v>
+        <v>7060315</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -6227,7 +6227,7 @@
         <v>125598485</v>
       </c>
       <c r="B59" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>125598483</v>
       </c>
       <c r="B60" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>125598484</v>
       </c>
       <c r="B61" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -6227,7 +6227,7 @@
         <v>125598485</v>
       </c>
       <c r="B59" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>125598483</v>
       </c>
       <c r="B60" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>125598484</v>
       </c>
       <c r="B61" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125583945</v>
+        <v>125598453</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528032</v>
+        <v>528210</v>
       </c>
       <c r="R2" t="n">
-        <v>7060391</v>
+        <v>7060528</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125583900</v>
+        <v>125598564</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528145</v>
+        <v>528199</v>
       </c>
       <c r="R3" t="n">
-        <v>7060374</v>
+        <v>7060578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125583874</v>
+        <v>125598565</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528145</v>
+        <v>528018</v>
       </c>
       <c r="R4" t="n">
-        <v>7060374</v>
+        <v>7060178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125584089</v>
+        <v>125598517</v>
       </c>
       <c r="B5" t="n">
-        <v>79591</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527979</v>
+        <v>528033</v>
       </c>
       <c r="R5" t="n">
-        <v>7060369</v>
+        <v>7060297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125583923</v>
+        <v>125598478</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528032</v>
+        <v>528153</v>
       </c>
       <c r="R6" t="n">
-        <v>7060391</v>
+        <v>7060642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125583976</v>
+        <v>125598479</v>
       </c>
       <c r="B7" t="n">
-        <v>78732</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527984</v>
+        <v>528026</v>
       </c>
       <c r="R7" t="n">
-        <v>7060282</v>
+        <v>7060285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125583954</v>
+        <v>125598480</v>
       </c>
       <c r="B8" t="n">
-        <v>92720</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527986</v>
+        <v>528047</v>
       </c>
       <c r="R8" t="n">
-        <v>7060380</v>
+        <v>7060306</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125583966</v>
+        <v>125598558</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527984</v>
+        <v>528156</v>
       </c>
       <c r="R9" t="n">
-        <v>7060282</v>
+        <v>7060663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125583851</v>
+        <v>125598559</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528097</v>
+        <v>528154</v>
       </c>
       <c r="R10" t="n">
-        <v>7060477</v>
+        <v>7060576</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1548,49 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125583819</v>
+        <v>125598560</v>
       </c>
       <c r="B11" t="n">
-        <v>92528</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528247</v>
+        <v>527902</v>
       </c>
       <c r="R11" t="n">
-        <v>7060540</v>
+        <v>7060225</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1617,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1649,45 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125583910</v>
+        <v>125598538</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stortjärnen, Jmt</t>
+          <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528115</v>
+        <v>528219</v>
       </c>
       <c r="R12" t="n">
-        <v>7060349</v>
+        <v>7060602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1714,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1746,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598443</v>
+        <v>125598539</v>
       </c>
       <c r="B13" t="n">
-        <v>75068</v>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528204</v>
+        <v>528155</v>
       </c>
       <c r="R13" t="n">
-        <v>7060474</v>
+        <v>7060497</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598442</v>
+        <v>125598540</v>
       </c>
       <c r="B14" t="n">
-        <v>75068</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1881,7 +1877,7 @@
         <v>528139</v>
       </c>
       <c r="R14" t="n">
-        <v>7060573</v>
+        <v>7060421</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598549</v>
+        <v>125598541</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>92083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528054</v>
+        <v>528123</v>
       </c>
       <c r="R15" t="n">
-        <v>7060352</v>
+        <v>7060390</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598540</v>
+        <v>125598542</v>
       </c>
       <c r="B16" t="n">
-        <v>91399</v>
+        <v>92083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528139</v>
+        <v>527984</v>
       </c>
       <c r="R16" t="n">
-        <v>7060421</v>
+        <v>7060358</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,45 +2130,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598569</v>
+        <v>125583954</v>
       </c>
       <c r="B17" t="n">
-        <v>92528</v>
+        <v>91962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528105</v>
+        <v>527986</v>
       </c>
       <c r="R17" t="n">
-        <v>7060384</v>
+        <v>7060380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2199,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2231,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598474</v>
+        <v>125598508</v>
       </c>
       <c r="B18" t="n">
-        <v>79562</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528004</v>
+        <v>528116</v>
       </c>
       <c r="R18" t="n">
-        <v>7060217</v>
+        <v>7060509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125598547</v>
+        <v>125583819</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2339,34 +2335,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528196</v>
+        <v>528247</v>
       </c>
       <c r="R19" t="n">
-        <v>7060721</v>
+        <v>7060540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2425,14 +2425,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598568</v>
+        <v>125598567</v>
       </c>
       <c r="B20" t="n">
-        <v>92528</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528100</v>
+        <v>528156</v>
       </c>
       <c r="R20" t="n">
-        <v>7060507</v>
+        <v>7060538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598445</v>
+        <v>125598568</v>
       </c>
       <c r="B21" t="n">
-        <v>75068</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527906</v>
+        <v>528100</v>
       </c>
       <c r="R21" t="n">
-        <v>7060232</v>
+        <v>7060507</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125598578</v>
+        <v>125598569</v>
       </c>
       <c r="B22" t="n">
-        <v>77922</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,21 +2630,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2657,7 +2657,7 @@
         <v>528105</v>
       </c>
       <c r="R22" t="n">
-        <v>7060313</v>
+        <v>7060384</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125598462</v>
+        <v>125598571</v>
       </c>
       <c r="B23" t="n">
-        <v>79591</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528155</v>
+        <v>527968</v>
       </c>
       <c r="R23" t="n">
-        <v>7060516</v>
+        <v>7060326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,14 +2813,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125598567</v>
+        <v>125598572</v>
       </c>
       <c r="B24" t="n">
-        <v>92528</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528156</v>
+        <v>528018</v>
       </c>
       <c r="R24" t="n">
-        <v>7060538</v>
+        <v>7060189</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,32 +2910,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598538</v>
+        <v>125598573</v>
       </c>
       <c r="B25" t="n">
-        <v>91399</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528219</v>
+        <v>527916</v>
       </c>
       <c r="R25" t="n">
-        <v>7060602</v>
+        <v>7060212</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598530</v>
+        <v>125598547</v>
       </c>
       <c r="B26" t="n">
-        <v>78731</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528109</v>
+        <v>528196</v>
       </c>
       <c r="R26" t="n">
-        <v>7060312</v>
+        <v>7060721</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598513</v>
+        <v>125598549</v>
       </c>
       <c r="B27" t="n">
-        <v>79980</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528117</v>
+        <v>528054</v>
       </c>
       <c r="R27" t="n">
-        <v>7060478</v>
+        <v>7060352</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598472</v>
+        <v>125598550</v>
       </c>
       <c r="B28" t="n">
-        <v>79562</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528108</v>
+        <v>528067</v>
       </c>
       <c r="R28" t="n">
-        <v>7060311</v>
+        <v>7060280</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,32 +3298,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598573</v>
+        <v>125598551</v>
       </c>
       <c r="B29" t="n">
-        <v>92528</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527916</v>
+        <v>528012</v>
       </c>
       <c r="R29" t="n">
-        <v>7060212</v>
+        <v>7060230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,32 +3395,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598478</v>
+        <v>125598552</v>
       </c>
       <c r="B30" t="n">
-        <v>91238</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528153</v>
+        <v>527891</v>
       </c>
       <c r="R30" t="n">
-        <v>7060642</v>
+        <v>7060221</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598533</v>
+        <v>125598442</v>
       </c>
       <c r="B31" t="n">
-        <v>78731</v>
+        <v>83307</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3503,21 +3503,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527893</v>
+        <v>528139</v>
       </c>
       <c r="R31" t="n">
-        <v>7060200</v>
+        <v>7060573</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598506</v>
+        <v>125598443</v>
       </c>
       <c r="B32" t="n">
-        <v>57812</v>
+        <v>83307</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3600,50 +3600,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528169</v>
+        <v>528204</v>
       </c>
       <c r="R32" t="n">
-        <v>7060483</v>
+        <v>7060474</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3702,32 +3686,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598565</v>
+        <v>125598445</v>
       </c>
       <c r="B33" t="n">
-        <v>91499</v>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3737,10 +3721,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528018</v>
+        <v>527906</v>
       </c>
       <c r="R33" t="n">
-        <v>7060178</v>
+        <v>7060232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3799,10 +3783,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598560</v>
+        <v>125598447</v>
       </c>
       <c r="B34" t="n">
-        <v>82785</v>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3810,21 +3794,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3834,10 +3818,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527902</v>
+        <v>527877</v>
       </c>
       <c r="R34" t="n">
-        <v>7060225</v>
+        <v>7060212</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,45 +3880,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598571</v>
+        <v>125583851</v>
       </c>
       <c r="B35" t="n">
-        <v>92528</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527968</v>
+        <v>528097</v>
       </c>
       <c r="R35" t="n">
-        <v>7060326</v>
+        <v>7060477</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3961,12 +3945,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3993,10 +3977,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598531</v>
+        <v>125583874</v>
       </c>
       <c r="B36" t="n">
-        <v>78731</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4024,14 +4008,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527988</v>
+        <v>528145</v>
       </c>
       <c r="R36" t="n">
-        <v>7060369</v>
+        <v>7060374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,12 +4042,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4090,10 +4074,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598559</v>
+        <v>125583910</v>
       </c>
       <c r="B37" t="n">
-        <v>82785</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4101,34 +4085,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528154</v>
+        <v>528115</v>
       </c>
       <c r="R37" t="n">
-        <v>7060576</v>
+        <v>7060349</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4155,12 +4139,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4187,10 +4171,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598453</v>
+        <v>125583923</v>
       </c>
       <c r="B38" t="n">
-        <v>96598</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4198,34 +4182,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528210</v>
+        <v>528032</v>
       </c>
       <c r="R38" t="n">
-        <v>7060528</v>
+        <v>7060391</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4252,12 +4236,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4284,10 +4268,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598551</v>
+        <v>125583966</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4295,34 +4279,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528012</v>
+        <v>527984</v>
       </c>
       <c r="R39" t="n">
-        <v>7060230</v>
+        <v>7060282</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4349,12 +4333,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4381,32 +4365,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598539</v>
+        <v>125598530</v>
       </c>
       <c r="B40" t="n">
-        <v>91399</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4416,10 +4400,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528155</v>
+        <v>528109</v>
       </c>
       <c r="R40" t="n">
-        <v>7060497</v>
+        <v>7060312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4478,10 +4462,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598552</v>
+        <v>125598531</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4473,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4497,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527891</v>
+        <v>527988</v>
       </c>
       <c r="R41" t="n">
-        <v>7060221</v>
+        <v>7060369</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4559,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598473</v>
+        <v>125598532</v>
       </c>
       <c r="B42" t="n">
-        <v>79562</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4570,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4594,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527959</v>
+        <v>528019</v>
       </c>
       <c r="R42" t="n">
-        <v>7060315</v>
+        <v>7060293</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4656,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598479</v>
+        <v>125598533</v>
       </c>
       <c r="B43" t="n">
-        <v>91238</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,21 +4667,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4707,10 +4691,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528026</v>
+        <v>527893</v>
       </c>
       <c r="R43" t="n">
-        <v>7060285</v>
+        <v>7060200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,10 +4753,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598532</v>
+        <v>125584089</v>
       </c>
       <c r="B44" t="n">
-        <v>78731</v>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,34 +4764,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528019</v>
+        <v>527979</v>
       </c>
       <c r="R44" t="n">
-        <v>7060293</v>
+        <v>7060369</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4834,12 +4818,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,10 +4850,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598517</v>
+        <v>125598462</v>
       </c>
       <c r="B45" t="n">
-        <v>91534</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4861,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4885,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528033</v>
+        <v>528155</v>
       </c>
       <c r="R45" t="n">
-        <v>7060297</v>
+        <v>7060516</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,32 +4947,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598564</v>
+        <v>125598463</v>
       </c>
       <c r="B46" t="n">
-        <v>91499</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +4982,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528199</v>
+        <v>527988</v>
       </c>
       <c r="R46" t="n">
-        <v>7060578</v>
+        <v>7060368</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5044,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598480</v>
+        <v>125598464</v>
       </c>
       <c r="B47" t="n">
-        <v>91238</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5055,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5079,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528047</v>
+        <v>528013</v>
       </c>
       <c r="R47" t="n">
-        <v>7060306</v>
+        <v>7060176</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,32 +5141,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598471</v>
+        <v>125598513</v>
       </c>
       <c r="B48" t="n">
-        <v>79562</v>
+        <v>80336</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5192,10 +5176,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528115</v>
+        <v>528117</v>
       </c>
       <c r="R48" t="n">
-        <v>7060370</v>
+        <v>7060478</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5254,32 +5238,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598469</v>
+        <v>125598514</v>
       </c>
       <c r="B49" t="n">
-        <v>79562</v>
+        <v>80336</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5289,10 +5273,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528156</v>
+        <v>527889</v>
       </c>
       <c r="R49" t="n">
-        <v>7060452</v>
+        <v>7060255</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5351,10 +5335,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598463</v>
+        <v>125598577</v>
       </c>
       <c r="B50" t="n">
-        <v>79591</v>
+        <v>78334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,21 +5346,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5370,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527988</v>
+        <v>528153</v>
       </c>
       <c r="R50" t="n">
-        <v>7060368</v>
+        <v>7060448</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5448,10 +5432,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598558</v>
+        <v>125598578</v>
       </c>
       <c r="B51" t="n">
-        <v>82785</v>
+        <v>78334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5443,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5467,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528156</v>
+        <v>528105</v>
       </c>
       <c r="R51" t="n">
-        <v>7060663</v>
+        <v>7060313</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5545,32 +5529,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598572</v>
+        <v>125598483</v>
       </c>
       <c r="B52" t="n">
-        <v>92528</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5580,10 +5564,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528018</v>
+        <v>528196</v>
       </c>
       <c r="R52" t="n">
-        <v>7060189</v>
+        <v>7060457</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5616,6 +5600,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5642,10 +5631,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125598508</v>
+        <v>125598484</v>
       </c>
       <c r="B53" t="n">
-        <v>80077</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5653,21 +5642,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5677,10 +5666,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528116</v>
+        <v>528028</v>
       </c>
       <c r="R53" t="n">
-        <v>7060509</v>
+        <v>7060282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5713,6 +5702,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5739,10 +5733,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598550</v>
+        <v>125598485</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5744,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5768,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528067</v>
+        <v>528035</v>
       </c>
       <c r="R54" t="n">
-        <v>7060280</v>
+        <v>7060278</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5810,6 +5804,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5836,10 +5835,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598464</v>
+        <v>125598486</v>
       </c>
       <c r="B55" t="n">
-        <v>79591</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5846,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,10 +5870,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528013</v>
+        <v>527875</v>
       </c>
       <c r="R55" t="n">
-        <v>7060176</v>
+        <v>7060218</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5907,6 +5906,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5933,10 +5937,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598470</v>
+        <v>125598506</v>
       </c>
       <c r="B56" t="n">
-        <v>79562</v>
+        <v>58114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5944,34 +5948,50 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Småvattenån, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528137</v>
+        <v>528169</v>
       </c>
       <c r="R56" t="n">
-        <v>7060400</v>
+        <v>7060483</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6030,45 +6050,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598541</v>
+        <v>125583900</v>
       </c>
       <c r="B57" t="n">
-        <v>91399</v>
+        <v>79085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528123</v>
+        <v>528145</v>
       </c>
       <c r="R57" t="n">
-        <v>7060390</v>
+        <v>7060374</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6095,12 +6115,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6127,45 +6147,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598542</v>
+        <v>125583945</v>
       </c>
       <c r="B58" t="n">
-        <v>91399</v>
+        <v>79085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527984</v>
+        <v>528032</v>
       </c>
       <c r="R58" t="n">
-        <v>7060358</v>
+        <v>7060391</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6192,12 +6212,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6224,10 +6244,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125598485</v>
+        <v>125583976</v>
       </c>
       <c r="B59" t="n">
-        <v>57657</v>
+        <v>79085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6235,34 +6255,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Småvattenån, Jmt</t>
+          <t>Stortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528035</v>
+        <v>527984</v>
       </c>
       <c r="R59" t="n">
-        <v>7060278</v>
+        <v>7060282</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6289,17 +6309,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6326,10 +6341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125598483</v>
+        <v>125598469</v>
       </c>
       <c r="B60" t="n">
-        <v>57657</v>
+        <v>79917</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6337,21 +6352,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6361,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528196</v>
+        <v>528156</v>
       </c>
       <c r="R60" t="n">
-        <v>7060457</v>
+        <v>7060452</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6397,11 +6412,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6428,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125598484</v>
+        <v>125598470</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>79917</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6439,21 +6449,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6463,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528028</v>
+        <v>528137</v>
       </c>
       <c r="R61" t="n">
-        <v>7060282</v>
+        <v>7060400</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6501,11 +6511,6 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6527,6 +6532,394 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125598471</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>528115</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7060370</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125598472</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>528108</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7060311</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125598473</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>527959</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7060315</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125598474</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>528004</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7060217</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19512-2025 artfynd.xlsx
+++ b/artfynd/A 19512-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598564</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598565</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598478</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598479</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598480</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598558</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598559</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598560</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598538</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598539</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598540</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598541</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598542</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583954</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598508</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583819</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2519,6 +2614,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598567</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2616,6 +2716,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598568</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598569</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2810,6 +2920,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598571</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2907,6 +3022,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598572</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3004,6 +3124,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598573</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3101,6 +3226,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598547</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3198,6 +3328,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598549</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3295,6 +3430,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598550</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3392,6 +3532,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598551</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3489,6 +3634,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598552</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3586,6 +3736,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598442</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3683,6 +3838,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598443</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3780,6 +3940,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598445</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3877,6 +4042,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598447</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3974,6 +4144,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583851</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4071,6 +4246,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583874</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4168,6 +4348,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583910</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4265,6 +4450,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583923</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4362,6 +4552,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583966</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4459,6 +4654,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598530</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4556,6 +4756,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598531</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4653,6 +4858,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598532</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4750,6 +4960,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598533</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4847,6 +5062,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125584089</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4944,6 +5164,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598462</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5041,6 +5266,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598463</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5138,6 +5368,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598464</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5235,6 +5470,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598513</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5332,6 +5572,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598514</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5429,6 +5674,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598577</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5526,6 +5776,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598578</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5628,6 +5883,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598483</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5730,6 +5990,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598484</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5832,6 +6097,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598485</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5934,6 +6204,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598486</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6047,6 +6322,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598506</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6144,6 +6424,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583900</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6241,6 +6526,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583945</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6338,6 +6628,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125583976</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6435,6 +6730,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598469</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6532,6 +6832,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598470</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6629,6 +6934,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598471</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6726,6 +7036,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598472</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6823,6 +7138,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598473</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6920,8 +7240,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598474</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>